--- a/output/Ekologia_kalkulator.xlsx
+++ b/output/Ekologia_kalkulator.xlsx
@@ -1187,7 +1187,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Trend stężeń - Slot 6</a:t>
+              <a:t>Trend stężeń - BENZEN</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3516,8 +3516,16 @@
           <t>Zanieczyszczenie 6</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr"/>
-      <c r="C87" s="8" t="inlineStr"/>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>BENZEN</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>benzen</t>
+        </is>
+      </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
           <t>µg/m3</t>
@@ -3556,90 +3564,150 @@
         <f>$B$2+0</f>
         <v/>
       </c>
-      <c r="B89" s="6" t="n"/>
-      <c r="C89" s="6" t="n"/>
-      <c r="D89" s="6" t="n"/>
+      <c r="B89" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C89" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D89" s="6" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5">
         <f>$B$2+1</f>
         <v/>
       </c>
-      <c r="B90" s="6" t="n"/>
-      <c r="C90" s="6" t="n"/>
-      <c r="D90" s="6" t="n"/>
+      <c r="B90" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C90" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" s="6" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5">
         <f>$B$2+2</f>
         <v/>
       </c>
-      <c r="B91" s="6" t="n"/>
-      <c r="C91" s="6" t="n"/>
-      <c r="D91" s="6" t="n"/>
+      <c r="B91" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C91" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D91" s="6" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5">
         <f>$B$2+3</f>
         <v/>
       </c>
-      <c r="B92" s="6" t="n"/>
-      <c r="C92" s="6" t="n"/>
-      <c r="D92" s="6" t="n"/>
+      <c r="B92" s="6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C92" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D92" s="6" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5">
         <f>$B$2+4</f>
         <v/>
       </c>
-      <c r="B93" s="6" t="n"/>
-      <c r="C93" s="6" t="n"/>
-      <c r="D93" s="6" t="n"/>
+      <c r="B93" s="6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C93" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D93" s="6" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5">
         <f>$B$2+5</f>
         <v/>
       </c>
-      <c r="B94" s="6" t="n"/>
-      <c r="C94" s="6" t="n"/>
-      <c r="D94" s="6" t="n"/>
+      <c r="B94" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C94" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D94" s="6" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5">
         <f>$B$2+6</f>
         <v/>
       </c>
-      <c r="B95" s="6" t="n"/>
-      <c r="C95" s="6" t="n"/>
-      <c r="D95" s="6" t="n"/>
+      <c r="B95" s="6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C95" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" s="6" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="5">
         <f>$B$2+7</f>
         <v/>
       </c>
-      <c r="B96" s="6" t="n"/>
-      <c r="C96" s="6" t="n"/>
-      <c r="D96" s="6" t="n"/>
+      <c r="B96" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C96" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D96" s="6" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5">
         <f>$B$2+8</f>
         <v/>
       </c>
-      <c r="B97" s="6" t="n"/>
-      <c r="C97" s="6" t="n"/>
-      <c r="D97" s="6" t="n"/>
+      <c r="B97" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C97" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D97" s="6" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5">
         <f>$B$2+9</f>
         <v/>
       </c>
-      <c r="B98" s="6" t="n"/>
-      <c r="C98" s="6" t="n"/>
-      <c r="D98" s="6" t="n"/>
+      <c r="B98" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C98" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D98" s="6" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
@@ -4549,15 +4617,15 @@
         <v/>
       </c>
       <c r="J10" s="12">
-        <f>IF(COUNTA(B14:B23)=0,"",MIN(B14:B23))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!B14:B23)=0,"",MIN('Powietrze_Dane'!B14:B23))</f>
         <v/>
       </c>
       <c r="K10" s="12">
-        <f>IF(COUNTA(B14:B23)=0,"",AVERAGE(B14:B23))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!B14:B23)=0,"",AVERAGE('Powietrze_Dane'!B14:B23))</f>
         <v/>
       </c>
       <c r="L10" s="12">
-        <f>IF(COUNTA(B14:B23)=0,"",MAX(B14:B23))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!B14:B23)=0,"",MAX('Powietrze_Dane'!B14:B23))</f>
         <v/>
       </c>
       <c r="M10" s="12">
@@ -4636,15 +4704,15 @@
         <v/>
       </c>
       <c r="J11" s="12">
-        <f>IF(COUNTA(C14:C23)=0,"",MIN(C14:C23))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!C14:C23)=0,"",MIN('Powietrze_Dane'!C14:C23))</f>
         <v/>
       </c>
       <c r="K11" s="12">
-        <f>IF(COUNTA(C14:C23)=0,"",AVERAGE(C14:C23))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!C14:C23)=0,"",AVERAGE('Powietrze_Dane'!C14:C23))</f>
         <v/>
       </c>
       <c r="L11" s="12">
-        <f>IF(COUNTA(C14:C23)=0,"",MAX(C14:C23))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!C14:C23)=0,"",MAX('Powietrze_Dane'!C14:C23))</f>
         <v/>
       </c>
       <c r="M11" s="12">
@@ -4723,15 +4791,15 @@
         <v/>
       </c>
       <c r="J12" s="12">
-        <f>IF(COUNTA(D14:D23)=0,"",MIN(D14:D23))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!D14:D23)=0,"",MIN('Powietrze_Dane'!D14:D23))</f>
         <v/>
       </c>
       <c r="K12" s="12">
-        <f>IF(COUNTA(D14:D23)=0,"",AVERAGE(D14:D23))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!D14:D23)=0,"",AVERAGE('Powietrze_Dane'!D14:D23))</f>
         <v/>
       </c>
       <c r="L12" s="12">
-        <f>IF(COUNTA(D14:D23)=0,"",MAX(D14:D23))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!D14:D23)=0,"",MAX('Powietrze_Dane'!D14:D23))</f>
         <v/>
       </c>
       <c r="M12" s="12">
@@ -4810,15 +4878,15 @@
         <v/>
       </c>
       <c r="J13" s="12">
-        <f>IF(COUNTA(B29:B38)=0,"",MIN(B29:B38))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!B29:B38)=0,"",MIN('Powietrze_Dane'!B29:B38))</f>
         <v/>
       </c>
       <c r="K13" s="12">
-        <f>IF(COUNTA(B29:B38)=0,"",AVERAGE(B29:B38))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!B29:B38)=0,"",AVERAGE('Powietrze_Dane'!B29:B38))</f>
         <v/>
       </c>
       <c r="L13" s="12">
-        <f>IF(COUNTA(B29:B38)=0,"",MAX(B29:B38))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!B29:B38)=0,"",MAX('Powietrze_Dane'!B29:B38))</f>
         <v/>
       </c>
       <c r="M13" s="12">
@@ -4897,15 +4965,15 @@
         <v/>
       </c>
       <c r="J14" s="12">
-        <f>IF(COUNTA(C29:C38)=0,"",MIN(C29:C38))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!C29:C38)=0,"",MIN('Powietrze_Dane'!C29:C38))</f>
         <v/>
       </c>
       <c r="K14" s="12">
-        <f>IF(COUNTA(C29:C38)=0,"",AVERAGE(C29:C38))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!C29:C38)=0,"",AVERAGE('Powietrze_Dane'!C29:C38))</f>
         <v/>
       </c>
       <c r="L14" s="12">
-        <f>IF(COUNTA(C29:C38)=0,"",MAX(C29:C38))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!C29:C38)=0,"",MAX('Powietrze_Dane'!C29:C38))</f>
         <v/>
       </c>
       <c r="M14" s="12">
@@ -4984,15 +5052,15 @@
         <v/>
       </c>
       <c r="J15" s="12">
-        <f>IF(COUNTA(D29:D38)=0,"",MIN(D29:D38))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!D29:D38)=0,"",MIN('Powietrze_Dane'!D29:D38))</f>
         <v/>
       </c>
       <c r="K15" s="12">
-        <f>IF(COUNTA(D29:D38)=0,"",AVERAGE(D29:D38))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!D29:D38)=0,"",AVERAGE('Powietrze_Dane'!D29:D38))</f>
         <v/>
       </c>
       <c r="L15" s="12">
-        <f>IF(COUNTA(D29:D38)=0,"",MAX(D29:D38))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!D29:D38)=0,"",MAX('Powietrze_Dane'!D29:D38))</f>
         <v/>
       </c>
       <c r="M15" s="12">
@@ -5071,15 +5139,15 @@
         <v/>
       </c>
       <c r="J16" s="12">
-        <f>IF(COUNTA(B44:B53)=0,"",MIN(B44:B53))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!B44:B53)=0,"",MIN('Powietrze_Dane'!B44:B53))</f>
         <v/>
       </c>
       <c r="K16" s="12">
-        <f>IF(COUNTA(B44:B53)=0,"",AVERAGE(B44:B53))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!B44:B53)=0,"",AVERAGE('Powietrze_Dane'!B44:B53))</f>
         <v/>
       </c>
       <c r="L16" s="12">
-        <f>IF(COUNTA(B44:B53)=0,"",MAX(B44:B53))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!B44:B53)=0,"",MAX('Powietrze_Dane'!B44:B53))</f>
         <v/>
       </c>
       <c r="M16" s="12">
@@ -5158,15 +5226,15 @@
         <v/>
       </c>
       <c r="J17" s="12">
-        <f>IF(COUNTA(C44:C53)=0,"",MIN(C44:C53))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!C44:C53)=0,"",MIN('Powietrze_Dane'!C44:C53))</f>
         <v/>
       </c>
       <c r="K17" s="12">
-        <f>IF(COUNTA(C44:C53)=0,"",AVERAGE(C44:C53))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!C44:C53)=0,"",AVERAGE('Powietrze_Dane'!C44:C53))</f>
         <v/>
       </c>
       <c r="L17" s="12">
-        <f>IF(COUNTA(C44:C53)=0,"",MAX(C44:C53))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!C44:C53)=0,"",MAX('Powietrze_Dane'!C44:C53))</f>
         <v/>
       </c>
       <c r="M17" s="12">
@@ -5245,15 +5313,15 @@
         <v/>
       </c>
       <c r="J18" s="12">
-        <f>IF(COUNTA(D44:D53)=0,"",MIN(D44:D53))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!D44:D53)=0,"",MIN('Powietrze_Dane'!D44:D53))</f>
         <v/>
       </c>
       <c r="K18" s="12">
-        <f>IF(COUNTA(D44:D53)=0,"",AVERAGE(D44:D53))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!D44:D53)=0,"",AVERAGE('Powietrze_Dane'!D44:D53))</f>
         <v/>
       </c>
       <c r="L18" s="12">
-        <f>IF(COUNTA(D44:D53)=0,"",MAX(D44:D53))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!D44:D53)=0,"",MAX('Powietrze_Dane'!D44:D53))</f>
         <v/>
       </c>
       <c r="M18" s="12">
@@ -5332,15 +5400,15 @@
         <v/>
       </c>
       <c r="J19" s="12">
-        <f>IF(COUNTA(B59:B68)=0,"",MIN(B59:B68))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!B59:B68)=0,"",MIN('Powietrze_Dane'!B59:B68))</f>
         <v/>
       </c>
       <c r="K19" s="12">
-        <f>IF(COUNTA(B59:B68)=0,"",AVERAGE(B59:B68))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!B59:B68)=0,"",AVERAGE('Powietrze_Dane'!B59:B68))</f>
         <v/>
       </c>
       <c r="L19" s="12">
-        <f>IF(COUNTA(B59:B68)=0,"",MAX(B59:B68))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!B59:B68)=0,"",MAX('Powietrze_Dane'!B59:B68))</f>
         <v/>
       </c>
       <c r="M19" s="12">
@@ -5419,15 +5487,15 @@
         <v/>
       </c>
       <c r="J20" s="12">
-        <f>IF(COUNTA(C59:C68)=0,"",MIN(C59:C68))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!C59:C68)=0,"",MIN('Powietrze_Dane'!C59:C68))</f>
         <v/>
       </c>
       <c r="K20" s="12">
-        <f>IF(COUNTA(C59:C68)=0,"",AVERAGE(C59:C68))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!C59:C68)=0,"",AVERAGE('Powietrze_Dane'!C59:C68))</f>
         <v/>
       </c>
       <c r="L20" s="12">
-        <f>IF(COUNTA(C59:C68)=0,"",MAX(C59:C68))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!C59:C68)=0,"",MAX('Powietrze_Dane'!C59:C68))</f>
         <v/>
       </c>
       <c r="M20" s="12">
@@ -5506,15 +5574,15 @@
         <v/>
       </c>
       <c r="J21" s="12">
-        <f>IF(COUNTA(D59:D68)=0,"",MIN(D59:D68))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!D59:D68)=0,"",MIN('Powietrze_Dane'!D59:D68))</f>
         <v/>
       </c>
       <c r="K21" s="12">
-        <f>IF(COUNTA(D59:D68)=0,"",AVERAGE(D59:D68))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!D59:D68)=0,"",AVERAGE('Powietrze_Dane'!D59:D68))</f>
         <v/>
       </c>
       <c r="L21" s="12">
-        <f>IF(COUNTA(D59:D68)=0,"",MAX(D59:D68))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!D59:D68)=0,"",MAX('Powietrze_Dane'!D59:D68))</f>
         <v/>
       </c>
       <c r="M21" s="12">
@@ -5593,15 +5661,15 @@
         <v/>
       </c>
       <c r="J22" s="12">
-        <f>IF(COUNTA(B74:B83)=0,"",MIN(B74:B83))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!B74:B83)=0,"",MIN('Powietrze_Dane'!B74:B83))</f>
         <v/>
       </c>
       <c r="K22" s="12">
-        <f>IF(COUNTA(B74:B83)=0,"",AVERAGE(B74:B83))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!B74:B83)=0,"",AVERAGE('Powietrze_Dane'!B74:B83))</f>
         <v/>
       </c>
       <c r="L22" s="12">
-        <f>IF(COUNTA(B74:B83)=0,"",MAX(B74:B83))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!B74:B83)=0,"",MAX('Powietrze_Dane'!B74:B83))</f>
         <v/>
       </c>
       <c r="M22" s="12">
@@ -5680,15 +5748,15 @@
         <v/>
       </c>
       <c r="J23" s="12">
-        <f>IF(COUNTA(C74:C83)=0,"",MIN(C74:C83))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!C74:C83)=0,"",MIN('Powietrze_Dane'!C74:C83))</f>
         <v/>
       </c>
       <c r="K23" s="12">
-        <f>IF(COUNTA(C74:C83)=0,"",AVERAGE(C74:C83))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!C74:C83)=0,"",AVERAGE('Powietrze_Dane'!C74:C83))</f>
         <v/>
       </c>
       <c r="L23" s="12">
-        <f>IF(COUNTA(C74:C83)=0,"",MAX(C74:C83))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!C74:C83)=0,"",MAX('Powietrze_Dane'!C74:C83))</f>
         <v/>
       </c>
       <c r="M23" s="12">
@@ -5767,15 +5835,15 @@
         <v/>
       </c>
       <c r="J24" s="12">
-        <f>IF(COUNTA(D74:D83)=0,"",MIN(D74:D83))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!D74:D83)=0,"",MIN('Powietrze_Dane'!D74:D83))</f>
         <v/>
       </c>
       <c r="K24" s="12">
-        <f>IF(COUNTA(D74:D83)=0,"",AVERAGE(D74:D83))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!D74:D83)=0,"",AVERAGE('Powietrze_Dane'!D74:D83))</f>
         <v/>
       </c>
       <c r="L24" s="12">
-        <f>IF(COUNTA(D74:D83)=0,"",MAX(D74:D83))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!D74:D83)=0,"",MAX('Powietrze_Dane'!D74:D83))</f>
         <v/>
       </c>
       <c r="M24" s="12">
@@ -5854,15 +5922,15 @@
         <v/>
       </c>
       <c r="J25" s="12">
-        <f>IF(COUNTA(B89:B98)=0,"",MIN(B89:B98))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!B89:B98)=0,"",MIN('Powietrze_Dane'!B89:B98))</f>
         <v/>
       </c>
       <c r="K25" s="12">
-        <f>IF(COUNTA(B89:B98)=0,"",AVERAGE(B89:B98))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!B89:B98)=0,"",AVERAGE('Powietrze_Dane'!B89:B98))</f>
         <v/>
       </c>
       <c r="L25" s="12">
-        <f>IF(COUNTA(B89:B98)=0,"",MAX(B89:B98))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!B89:B98)=0,"",MAX('Powietrze_Dane'!B89:B98))</f>
         <v/>
       </c>
       <c r="M25" s="12">
@@ -5941,15 +6009,15 @@
         <v/>
       </c>
       <c r="J26" s="12">
-        <f>IF(COUNTA(C89:C98)=0,"",MIN(C89:C98))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!C89:C98)=0,"",MIN('Powietrze_Dane'!C89:C98))</f>
         <v/>
       </c>
       <c r="K26" s="12">
-        <f>IF(COUNTA(C89:C98)=0,"",AVERAGE(C89:C98))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!C89:C98)=0,"",AVERAGE('Powietrze_Dane'!C89:C98))</f>
         <v/>
       </c>
       <c r="L26" s="12">
-        <f>IF(COUNTA(C89:C98)=0,"",MAX(C89:C98))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!C89:C98)=0,"",MAX('Powietrze_Dane'!C89:C98))</f>
         <v/>
       </c>
       <c r="M26" s="12">
@@ -6028,15 +6096,15 @@
         <v/>
       </c>
       <c r="J27" s="12">
-        <f>IF(COUNTA(D89:D98)=0,"",MIN(D89:D98))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!D89:D98)=0,"",MIN('Powietrze_Dane'!D89:D98))</f>
         <v/>
       </c>
       <c r="K27" s="12">
-        <f>IF(COUNTA(D89:D98)=0,"",AVERAGE(D89:D98))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!D89:D98)=0,"",AVERAGE('Powietrze_Dane'!D89:D98))</f>
         <v/>
       </c>
       <c r="L27" s="12">
-        <f>IF(COUNTA(D89:D98)=0,"",MAX(D89:D98))</f>
+        <f>IF(COUNTA('Powietrze_Dane'!D89:D98)=0,"",MAX('Powietrze_Dane'!D89:D98))</f>
         <v/>
       </c>
       <c r="M27" s="12">
@@ -6899,7 +6967,7 @@
         </is>
       </c>
       <c r="B5" s="11">
-        <f>Gleba_Wyniki!B5</f>
+        <f>Gleba_Wyniki!B4</f>
         <v/>
       </c>
     </row>
@@ -6910,7 +6978,7 @@
         </is>
       </c>
       <c r="B6" s="11">
-        <f>Gleba_Wyniki!B6</f>
+        <f>Gleba_Wyniki!B5</f>
         <v/>
       </c>
     </row>
@@ -6921,7 +6989,7 @@
         </is>
       </c>
       <c r="B7" s="11">
-        <f>Gleba_Wyniki!B7</f>
+        <f>Gleba_Wyniki!B6</f>
         <v/>
       </c>
     </row>
@@ -6932,7 +7000,7 @@
         </is>
       </c>
       <c r="B8" s="11">
-        <f>Gleba_Wyniki!B8</f>
+        <f>Gleba_Wyniki!B7</f>
         <v/>
       </c>
     </row>

--- a/output/Ekologia_kalkulator.xlsx
+++ b/output/Ekologia_kalkulator.xlsx
@@ -4383,11 +4383,11 @@
         <v/>
       </c>
       <c r="H3" s="12">
-        <f>COUNTIFS($B$10:$B$27,A3,$Q$10:$Q$27,"&lt;&gt;")</f>
+        <f>SUMPRODUCT(($B$10:$B$27=A3)*(LEN($Q$10:$Q$27)&gt;0))</f>
         <v/>
       </c>
       <c r="I3" s="12">
-        <f>COUNTIFS($B$10:$B$27,A3,$R$10:$R$27,"&lt;&gt;")</f>
+        <f>SUMPRODUCT(($B$10:$B$27=A3)*(LEN($R$10:$R$27)&gt;0))</f>
         <v/>
       </c>
     </row>
@@ -4422,11 +4422,11 @@
         <v/>
       </c>
       <c r="H4" s="12">
-        <f>COUNTIFS($B$10:$B$27,A4,$Q$10:$Q$27,"&lt;&gt;")</f>
+        <f>SUMPRODUCT(($B$10:$B$27=A4)*(LEN($Q$10:$Q$27)&gt;0))</f>
         <v/>
       </c>
       <c r="I4" s="12">
-        <f>COUNTIFS($B$10:$B$27,A4,$R$10:$R$27,"&lt;&gt;")</f>
+        <f>SUMPRODUCT(($B$10:$B$27=A4)*(LEN($R$10:$R$27)&gt;0))</f>
         <v/>
       </c>
     </row>
@@ -4461,11 +4461,11 @@
         <v/>
       </c>
       <c r="H5" s="12">
-        <f>COUNTIFS($B$10:$B$27,A5,$Q$10:$Q$27,"&lt;&gt;")</f>
+        <f>SUMPRODUCT(($B$10:$B$27=A5)*(LEN($Q$10:$Q$27)&gt;0))</f>
         <v/>
       </c>
       <c r="I5" s="12">
-        <f>COUNTIFS($B$10:$B$27,A5,$R$10:$R$27,"&lt;&gt;")</f>
+        <f>SUMPRODUCT(($B$10:$B$27=A5)*(LEN($R$10:$R$27)&gt;0))</f>
         <v/>
       </c>
     </row>

--- a/output/Ekologia_kalkulator.xlsx
+++ b/output/Ekologia_kalkulator.xlsx
@@ -3759,12 +3759,12 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Zanieczyszczenie</t>
+          <t>Substancja</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Współczynnik toksyczności</t>
+          <t>Limit D24 [µg/m3]</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">

--- a/output/Ekologia_kalkulator.xlsx
+++ b/output/Ekologia_kalkulator.xlsx
@@ -12,20 +12,24 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Powietrze_Mapowanie" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Powietrze_Wyniki" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Powietrze_Wykresy" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gleba_Dane" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gleba_Wyniki" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gleba_Wykresy" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprawozdanie_powietrze" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gleba_Dane" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gleba_Wyniki" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gleba_Wykresy" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprawozdanie_gleba" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Sprawozdanie_powietrze'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Sprawozdanie_gleba'!$1:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="dd.mm.yyyy"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd.mm.yyyy"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -52,7 +56,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -89,6 +93,16 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -116,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -125,11 +139,14 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -137,14 +154,17 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -231,21 +251,13 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="13"/>
+  <style val="2"/>
   <chart>
     <title>
       <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Trend stężeń - O3</a:t>
-            </a:r>
-          </a:p>
-        </rich>
+        <strRef>
+          <f>'Powietrze_Wykresy'!$N$2</f>
+        </strRef>
       </tx>
     </title>
     <plotArea>
@@ -258,18 +270,24 @@
             <v>miejska</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="24000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
-                <a:srgbClr val="2F6A48"/>
+                <a:srgbClr val="3B6FB6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="5"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="3B6FB6"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="3B6FB6"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -292,18 +310,24 @@
             <v>podmiejska</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="24000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
-                <a:srgbClr val="3F6B85"/>
+                <a:srgbClr val="4F8A5B"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="5"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4F8A5B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="4F8A5B"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -326,18 +350,24 @@
             <v>pozamiejska</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="24000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
-                <a:srgbClr val="A57845"/>
+                <a:srgbClr val="B57F3F"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="5"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="B57F3F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="B57F3F"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -362,7 +392,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -378,8 +407,17 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="dd.mm" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="B8C2CC"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="20"/>
       </valAx>
       <valAx>
@@ -388,7 +426,16 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E8EF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
@@ -398,7 +445,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Stężenie [µg/m3]</a:t>
+                  <a:t>Stężenie [jednostka]</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -406,35 +453,44 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="B8C2CC"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+      <a:solidFill>
+        <a:srgbClr val="D8DEE8"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="13"/>
+  <style val="2"/>
   <chart>
     <title>
       <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Trend stężeń - SO2</a:t>
-            </a:r>
-          </a:p>
-        </rich>
+        <strRef>
+          <f>'Powietrze_Wykresy'!$N$3</f>
+        </strRef>
       </tx>
     </title>
     <plotArea>
@@ -447,18 +503,24 @@
             <v>miejska</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="24000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
-                <a:srgbClr val="2F6A48"/>
+                <a:srgbClr val="3B6FB6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="5"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="3B6FB6"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="3B6FB6"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -481,18 +543,24 @@
             <v>podmiejska</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="24000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
-                <a:srgbClr val="3F6B85"/>
+                <a:srgbClr val="4F8A5B"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="5"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4F8A5B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="4F8A5B"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -515,18 +583,24 @@
             <v>pozamiejska</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="24000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
-                <a:srgbClr val="A57845"/>
+                <a:srgbClr val="B57F3F"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="5"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="B57F3F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="B57F3F"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -551,7 +625,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -567,8 +640,17 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="dd.mm" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="B8C2CC"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="20"/>
       </valAx>
       <valAx>
@@ -577,7 +659,16 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E8EF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
@@ -587,7 +678,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Stężenie [µg/m3]</a:t>
+                  <a:t>Stężenie [jednostka]</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -595,35 +686,44 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="B8C2CC"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+      <a:solidFill>
+        <a:srgbClr val="D8DEE8"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="13"/>
+  <style val="2"/>
   <chart>
     <title>
       <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Trend stężeń - NO2</a:t>
-            </a:r>
-          </a:p>
-        </rich>
+        <strRef>
+          <f>'Powietrze_Wykresy'!$N$4</f>
+        </strRef>
       </tx>
     </title>
     <plotArea>
@@ -636,18 +736,24 @@
             <v>miejska</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="24000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
-                <a:srgbClr val="2F6A48"/>
+                <a:srgbClr val="3B6FB6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="5"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="3B6FB6"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="3B6FB6"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -670,18 +776,24 @@
             <v>podmiejska</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="24000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
-                <a:srgbClr val="3F6B85"/>
+                <a:srgbClr val="4F8A5B"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="5"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4F8A5B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="4F8A5B"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -704,18 +816,24 @@
             <v>pozamiejska</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="24000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
-                <a:srgbClr val="A57845"/>
+                <a:srgbClr val="B57F3F"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="5"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="B57F3F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="B57F3F"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -740,7 +858,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -756,8 +873,17 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="dd.mm" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="B8C2CC"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="20"/>
       </valAx>
       <valAx>
@@ -766,7 +892,16 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E8EF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
@@ -776,7 +911,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Stężenie [µg/m3]</a:t>
+                  <a:t>Stężenie [jednostka]</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -784,35 +919,44 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="B8C2CC"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+      <a:solidFill>
+        <a:srgbClr val="D8DEE8"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="13"/>
+  <style val="2"/>
   <chart>
     <title>
       <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Trend stężeń - PM10</a:t>
-            </a:r>
-          </a:p>
-        </rich>
+        <strRef>
+          <f>'Powietrze_Wykresy'!$N$5</f>
+        </strRef>
       </tx>
     </title>
     <plotArea>
@@ -825,18 +969,24 @@
             <v>miejska</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="24000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
-                <a:srgbClr val="2F6A48"/>
+                <a:srgbClr val="3B6FB6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="5"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="3B6FB6"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="3B6FB6"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -859,18 +1009,24 @@
             <v>podmiejska</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="24000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
-                <a:srgbClr val="3F6B85"/>
+                <a:srgbClr val="4F8A5B"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="5"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4F8A5B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="4F8A5B"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -893,18 +1049,24 @@
             <v>pozamiejska</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="24000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
-                <a:srgbClr val="A57845"/>
+                <a:srgbClr val="B57F3F"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="5"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="B57F3F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="B57F3F"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -929,7 +1091,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -945,8 +1106,17 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="dd.mm" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="B8C2CC"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="20"/>
       </valAx>
       <valAx>
@@ -955,7 +1125,16 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E8EF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
@@ -965,7 +1144,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Stężenie [µg/m3]</a:t>
+                  <a:t>Stężenie [jednostka]</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -973,35 +1152,44 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="B8C2CC"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+      <a:solidFill>
+        <a:srgbClr val="D8DEE8"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="13"/>
+  <style val="2"/>
   <chart>
     <title>
       <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Trend stężeń - CO</a:t>
-            </a:r>
-          </a:p>
-        </rich>
+        <strRef>
+          <f>'Powietrze_Wykresy'!$N$6</f>
+        </strRef>
       </tx>
     </title>
     <plotArea>
@@ -1014,18 +1202,24 @@
             <v>miejska</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="24000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
-                <a:srgbClr val="2F6A48"/>
+                <a:srgbClr val="3B6FB6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="5"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="3B6FB6"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="3B6FB6"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1048,18 +1242,24 @@
             <v>podmiejska</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="24000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
-                <a:srgbClr val="3F6B85"/>
+                <a:srgbClr val="4F8A5B"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="5"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4F8A5B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="4F8A5B"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1082,18 +1282,24 @@
             <v>pozamiejska</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="24000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
-                <a:srgbClr val="A57845"/>
+                <a:srgbClr val="B57F3F"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="5"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="B57F3F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="B57F3F"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1118,7 +1324,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -1134,8 +1339,17 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="dd.mm" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="B8C2CC"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="20"/>
       </valAx>
       <valAx>
@@ -1144,7 +1358,16 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E8EF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
@@ -1154,7 +1377,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Stężenie [µg/m3]</a:t>
+                  <a:t>Stężenie [jednostka]</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1162,35 +1385,44 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="B8C2CC"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+      <a:solidFill>
+        <a:srgbClr val="D8DEE8"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="13"/>
+  <style val="2"/>
   <chart>
     <title>
       <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Trend stężeń - BENZEN</a:t>
-            </a:r>
-          </a:p>
-        </rich>
+        <strRef>
+          <f>'Powietrze_Wykresy'!$N$7</f>
+        </strRef>
       </tx>
     </title>
     <plotArea>
@@ -1203,18 +1435,24 @@
             <v>miejska</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="24000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
-                <a:srgbClr val="2F6A48"/>
+                <a:srgbClr val="3B6FB6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="5"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="3B6FB6"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="3B6FB6"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1237,18 +1475,24 @@
             <v>podmiejska</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="24000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
-                <a:srgbClr val="3F6B85"/>
+                <a:srgbClr val="4F8A5B"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="5"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4F8A5B"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="4F8A5B"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1271,18 +1515,24 @@
             <v>pozamiejska</v>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="24000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
-                <a:srgbClr val="A57845"/>
+                <a:srgbClr val="B57F3F"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="6"/>
+            <size val="5"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="B57F3F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="B57F3F"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1307,7 +1557,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -1323,8 +1572,17 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="dd.mm" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="B8C2CC"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="20"/>
       </valAx>
       <valAx>
@@ -1333,7 +1591,16 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E8EF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
@@ -1343,7 +1610,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Stężenie [µg/m3]</a:t>
+                  <a:t>Stężenie [jednostka]</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1351,21 +1618,38 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="B8C2CC"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+      <a:solidFill>
+        <a:srgbClr val="D8DEE8"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
+  <style val="2"/>
   <chart>
     <title>
       <tx>
@@ -1390,7 +1674,13 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="7AA6C2"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill>
+                <a:srgbClr val="5F8AA4"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1405,7 +1695,7 @@
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <gapWidth val="70"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -1417,6 +1707,14 @@
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="B8C2CC"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -1426,7 +1724,16 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E8EF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
@@ -1444,21 +1751,35 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="B8C2CC"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+      <a:solidFill>
+        <a:srgbClr val="D8DEE8"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
+  <style val="2"/>
   <chart>
     <title>
       <tx>
@@ -1483,7 +1804,13 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="7AA6C2"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill>
+                <a:srgbClr val="5F8AA4"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1498,7 +1825,7 @@
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <gapWidth val="70"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -1510,6 +1837,14 @@
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="B8C2CC"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -1519,7 +1854,16 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E8EF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
@@ -1537,21 +1881,35 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="B8C2CC"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+      <a:solidFill>
+        <a:srgbClr val="D8DEE8"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
+  <style val="2"/>
   <chart>
     <title>
       <tx>
@@ -1576,7 +1934,13 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="7AA6C2"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill>
+                <a:srgbClr val="5F8AA4"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1591,7 +1955,7 @@
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <gapWidth val="70"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -1603,6 +1967,14 @@
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="B8C2CC"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -1612,7 +1984,16 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E8EF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
@@ -1630,15 +2011,29 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+            <a:solidFill>
+              <a:srgbClr val="B8C2CC"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+      <a:solidFill>
+        <a:srgbClr val="D8DEE8"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1651,7 +2046,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3600000" cy="2520000"/>
+    <ext cx="3888000" cy="2736000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1673,7 +2068,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3600000" cy="2520000"/>
+    <ext cx="3888000" cy="2736000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1695,7 +2090,7 @@
       <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3600000" cy="2520000"/>
+    <ext cx="3888000" cy="2736000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -1717,7 +2112,7 @@
       <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3600000" cy="2520000"/>
+    <ext cx="3888000" cy="2736000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -1739,7 +2134,7 @@
       <row>35</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3600000" cy="2520000"/>
+    <ext cx="3888000" cy="2736000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -1761,7 +2156,7 @@
       <row>35</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3600000" cy="2520000"/>
+    <ext cx="3888000" cy="2736000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -1788,7 +2183,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3600000" cy="2520000"/>
+    <ext cx="3888000" cy="2736000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1810,7 +2205,7 @@
       <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3600000" cy="2520000"/>
+    <ext cx="3888000" cy="2736000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1832,7 +2227,7 @@
       <row>35</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3600000" cy="2520000"/>
+    <ext cx="3888000" cy="2736000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -2139,7 +2534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -2175,98 +2570,119 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Powietrze: wpisz alias zanieczyszczenia, nazwę, jednostkę i 10 kolejnych dni danych dla 3 stacji.</t>
+          <t>Workbook startuje z pustymi polami wejściowymi w arkuszach Powietrze_Dane i Gleba_Dane, aby można było od razu wpisać własne dane.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Gleba: wpisz surowe pomiary pH, objętości i stężenia. Arkusz wynikowy obliczy Hh, S, T, Mz, Hh_ha, CaO i CaCO3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Wzory zaimplementowane w workbooku:</t>
-        </is>
-      </c>
-    </row>
+          <t>Powietrze: wpisz alias zanieczyszczenia, nazwę, jednostkę i 10 kolejnych dni danych dla 3 stacji. Arkusz Sprawozdanie_powietrze pobiera z nich dane automatycznie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Gleba: wpisz surowe pomiary pH, objętości i stężenia. Arkusze wynikowe oraz Sprawozdanie_gleba uzupełniają się automatycznie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Psi = Σ(Cx / D24x)</t>
+          <t>Wzory zaimplementowane w workbooku:</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Tau = Σ(Cx * alpha_t)</t>
+          <t>Psi = Σ(Cx / D24x)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Hh = V * c * 10 * k</t>
+          <t>Tau = Σ(Cx * alpha_t)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Mz = p * h * rho</t>
+          <t>Hh = V * c * 10 * k</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Hh_ha = Hh * Mz / 100</t>
+          <t>Mz = p * h * rho</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>CaO = Hh_ha * 0,028</t>
+          <t>Hh_ha = Hh * Mz / 100</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>CaCO3 = Hh_ha * 0,050</t>
+          <t>CaO = Hh_ha * 0,028</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>S = (V * c - V1 * c1) * 4 * 5</t>
+          <t>CaCO3 = Hh_ha * 0,050</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>S = (V * c - V1 * c1) * 4 * 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>T = Hh + S</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Założenie: klasyfikacja gleby korzysta ze średniego pH badanej próbki w KCl.</t>
-        </is>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Arkusze Sprawozdanie_powietrze i Sprawozdanie_gleba są roboczym odwzorowaniem wzorów sprawozdań i zawierają pola automatyczne oraz ręczne.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Wykresy pozostają widoczne także przy pustych danych wejściowych. Trendline, równania i R² nie zostały dodane - openpyxl nie daje tu stabilnej kontroli przy seryjnym generowaniu wykresów.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Założenie: klasyfikacja gleby korzysta ze średniego pH badanej próbki w KCl.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Brakujących limitów i współczynników toksyczności nie uzupełniono automatycznie - workbook pokazuje wtedy ostrzeżenia.</t>
         </is>
@@ -2277,6 +2693,802 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ćwiczenie nr 2 - Parametry fizykochemiczne gleby</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Rok akademicki</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="n"/>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Grupa</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Zespół</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Zaliczenie</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="n"/>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Uwagi organizacyjne</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="n"/>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Skład zespołu badawczego</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Lp.</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Imię i nazwisko</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Rola w zespole</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Uwagi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Kwasowość czynna</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Przedmiot analizy</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Pomiar 1</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Pomiar 2</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Średnia</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10">
+        <f>Gleba_Dane!$A$5</f>
+        <v/>
+      </c>
+      <c r="B15" s="15">
+        <f>Gleba_Dane!$B$5</f>
+        <v/>
+      </c>
+      <c r="C15" s="15">
+        <f>Gleba_Dane!$C$5</f>
+        <v/>
+      </c>
+      <c r="D15" s="15">
+        <f>Gleba_Dane!$D$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10">
+        <f>Gleba_Dane!$A$6</f>
+        <v/>
+      </c>
+      <c r="B16" s="15">
+        <f>Gleba_Dane!$B$6</f>
+        <v/>
+      </c>
+      <c r="C16" s="15">
+        <f>Gleba_Dane!$C$6</f>
+        <v/>
+      </c>
+      <c r="D16" s="15">
+        <f>Gleba_Dane!$D$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Kwasowość wymienna</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Przedmiot analizy</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Pomiar 1</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Pomiar 2</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Średnia</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10">
+        <f>Gleba_Dane!$A$11</f>
+        <v/>
+      </c>
+      <c r="B20" s="15">
+        <f>Gleba_Dane!$B$11</f>
+        <v/>
+      </c>
+      <c r="C20" s="15">
+        <f>Gleba_Dane!$C$11</f>
+        <v/>
+      </c>
+      <c r="D20" s="15">
+        <f>Gleba_Dane!$D$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10">
+        <f>Gleba_Dane!$A$12</f>
+        <v/>
+      </c>
+      <c r="B21" s="15">
+        <f>Gleba_Dane!$B$12</f>
+        <v/>
+      </c>
+      <c r="C21" s="15">
+        <f>Gleba_Dane!$C$12</f>
+        <v/>
+      </c>
+      <c r="D21" s="15">
+        <f>Gleba_Dane!$D$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Kwasowość hydrolityczna</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Parametr</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Wartość</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Jednostka</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Uwagi</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>VNaOH</t>
+        </is>
+      </c>
+      <c r="B25" s="15">
+        <f>Gleba_Dane!$B$17</f>
+        <v/>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>cm3</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>c_NaOH</t>
+        </is>
+      </c>
+      <c r="B26" s="15">
+        <f>Gleba_Dane!$B$18</f>
+        <v/>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>mol/dm3</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="B27" s="15">
+        <f>Gleba_Dane!$B$19</f>
+        <v/>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>współczynnik</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>dobierz do rodzaju gleby</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Hh</t>
+        </is>
+      </c>
+      <c r="B28" s="15">
+        <f>Gleba_Wyniki!$B$8</f>
+        <v/>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>mmol(+)/100 g</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>wynik obliczeń</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Przebieg reakcji</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="n"/>
+    </row>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Obliczenia</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Wielkość</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Wartość</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Jednostka</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Komentarz</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Hh</t>
+        </is>
+      </c>
+      <c r="B37" s="15">
+        <f>Gleba_Wyniki!$B$8</f>
+        <v/>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>mmol(+)/100 g</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Mz</t>
+        </is>
+      </c>
+      <c r="B38" s="15">
+        <f>Gleba_Wyniki!$B$9</f>
+        <v/>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>wartość pomocnicza</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>Hh_ha</t>
+        </is>
+      </c>
+      <c r="B39" s="15">
+        <f>Gleba_Wyniki!$B$10</f>
+        <v/>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>mol(+)</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>wartość pomocnicza</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>CaO</t>
+        </is>
+      </c>
+      <c r="B40" s="15">
+        <f>Gleba_Wyniki!$B$11</f>
+        <v/>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>kg/ha</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>wartość pomocnicza</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>CaCO3</t>
+        </is>
+      </c>
+      <c r="B41" s="15">
+        <f>Gleba_Wyniki!$B$12</f>
+        <v/>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>kg/ha</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>wartość pomocnicza</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Stopień wysycenia kationami zasadowymi</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Parametr</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Wartość</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Jednostka</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Uwagi</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>V_HCl</t>
+        </is>
+      </c>
+      <c r="B45" s="15">
+        <f>Gleba_Dane!$B$24</f>
+        <v/>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>cm3</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>c_HCl</t>
+        </is>
+      </c>
+      <c r="B46" s="15">
+        <f>Gleba_Dane!$B$25</f>
+        <v/>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>mol/dm3</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>V1_NaOH</t>
+        </is>
+      </c>
+      <c r="B47" s="15">
+        <f>Gleba_Dane!$B$26</f>
+        <v/>
+      </c>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>cm3</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>c1_NaOH</t>
+        </is>
+      </c>
+      <c r="B48" s="15">
+        <f>Gleba_Dane!$B$27</f>
+        <v/>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>mol/dm3</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B49" s="15">
+        <f>Gleba_Wyniki!$B$13</f>
+        <v/>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t>mmol(+)/100 g</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>wynik obliczeń</t>
+        </is>
+      </c>
+    </row>
+    <row r="50"/>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>Przebieg reakcji</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="n"/>
+    </row>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>Pojemność sorpcyjna</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Wielkość</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Wartość</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>Jednostka</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Uwagi</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>Hh</t>
+        </is>
+      </c>
+      <c r="B58" s="15">
+        <f>Gleba_Wyniki!$B$8</f>
+        <v/>
+      </c>
+      <c r="C58" s="15" t="inlineStr">
+        <is>
+          <t>mmol(+)/100 g</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B59" s="15">
+        <f>Gleba_Wyniki!$B$13</f>
+        <v/>
+      </c>
+      <c r="C59" s="15" t="inlineStr">
+        <is>
+          <t>mmol(+)/100 g</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B60" s="15">
+        <f>Gleba_Wyniki!$B$14</f>
+        <v/>
+      </c>
+      <c r="C60" s="15" t="inlineStr">
+        <is>
+          <t>mmol(+)/100 g</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>wynik obliczeń</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>Klasa gleby uprawnej</t>
+        </is>
+      </c>
+      <c r="B61" s="15">
+        <f>Gleba_Wyniki!$B$15</f>
+        <v/>
+      </c>
+      <c r="C61" s="15" t="inlineStr"/>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>automatycznie</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>Klasa gleby leśnej</t>
+        </is>
+      </c>
+      <c r="B62" s="15">
+        <f>Gleba_Wyniki!$B$16</f>
+        <v/>
+      </c>
+      <c r="C62" s="15" t="inlineStr"/>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>automatycznie</t>
+        </is>
+      </c>
+    </row>
+    <row r="63"/>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>Interpretacja wyników</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="n"/>
+    </row>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A52:H54"/>
+    <mergeCell ref="A65:H69"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="A31:H33"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="H3:I3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2312,9 +3524,7 @@
           <t>Data początkowa</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
-        <v>46082</v>
-      </c>
+      <c r="B2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -2323,7 +3533,7 @@
         </is>
       </c>
       <c r="B3" s="5">
-        <f>B2+9</f>
+        <f>IF(B2="","",B2+9)</f>
         <v/>
       </c>
     </row>
@@ -2333,11 +3543,7 @@
           <t>Godzina pomiaru</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
+      <c r="B4" s="6" t="n"/>
     </row>
     <row r="5"/>
     <row r="6">
@@ -2373,26 +3579,10 @@
           <t>miejska</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>komunikacyjna</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>dolnośląskie</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>ul. Wyb. J. Conrada-Korzeniowskiego 18, Wrocław</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Stacja Wrocław - śródmieście</t>
-        </is>
-      </c>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -2400,26 +3590,10 @@
           <t>podmiejska</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>tło</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>dolnośląskie</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>ul. Parkowa 3, Długołęka</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>Stacja Długołęka</t>
-        </is>
-      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -2427,53 +3601,25 @@
           <t>pozamiejska</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>tło</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>dolnośląskie</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Jeleniów 12, teren referencyjny</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Stacja Jeleniów</t>
-        </is>
-      </c>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
     </row>
     <row r="10"/>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Zanieczyszczenie 1</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>O3</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>ozon</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>µg/m3</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>Wprowadź 10 kolejnych dni danych</t>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Uzupełnij alias, nazwę, jednostkę i 10 kolejnych dni danych</t>
         </is>
       </c>
     </row>
@@ -2501,153 +3647,93 @@
     </row>
     <row r="14">
       <c r="A14" s="5">
-        <f>$B$2+0</f>
-        <v/>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>65</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>50</v>
-      </c>
+        <f>IF($B$2="","",$B$2+0)</f>
+        <v/>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5">
-        <f>$B$2+1</f>
-        <v/>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>72</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>53</v>
-      </c>
+        <f>IF($B$2="","",$B$2+1)</f>
+        <v/>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5">
-        <f>$B$2+2</f>
-        <v/>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>57</v>
-      </c>
+        <f>IF($B$2="","",$B$2+2)</f>
+        <v/>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5">
-        <f>$B$2+3</f>
-        <v/>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>78</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>69</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>61</v>
-      </c>
+        <f>IF($B$2="","",$B$2+3)</f>
+        <v/>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5">
-        <f>$B$2+4</f>
-        <v/>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>74</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>67</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>59</v>
-      </c>
+        <f>IF($B$2="","",$B$2+4)</f>
+        <v/>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5">
-        <f>$B$2+5</f>
-        <v/>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>70</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>62</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>56</v>
-      </c>
+        <f>IF($B$2="","",$B$2+5)</f>
+        <v/>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5">
-        <f>$B$2+6</f>
-        <v/>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>54</v>
-      </c>
+        <f>IF($B$2="","",$B$2+6)</f>
+        <v/>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5">
-        <f>$B$2+7</f>
-        <v/>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>66</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>52</v>
-      </c>
+        <f>IF($B$2="","",$B$2+7)</f>
+        <v/>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5">
-        <f>$B$2+8</f>
-        <v/>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>64</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>56</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>49</v>
-      </c>
+        <f>IF($B$2="","",$B$2+8)</f>
+        <v/>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5">
-        <f>$B$2+9</f>
-        <v/>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>61</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>47</v>
-      </c>
+        <f>IF($B$2="","",$B$2+9)</f>
+        <v/>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -2656,36 +3742,24 @@
         </is>
       </c>
       <c r="B24" s="11">
-        <f>$B$4</f>
+        <f>IF($B$4="","",$B$4)</f>
         <v/>
       </c>
     </row>
     <row r="25"/>
     <row r="26"/>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>Zanieczyszczenie 2</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>SO2</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>ditlenek siarki</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>µg/m3</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="inlineStr">
-        <is>
-          <t>Wprowadź 10 kolejnych dni danych</t>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>Uzupełnij alias, nazwę, jednostkę i 10 kolejnych dni danych</t>
         </is>
       </c>
     </row>
@@ -2713,153 +3787,93 @@
     </row>
     <row r="29">
       <c r="A29" s="5">
-        <f>$B$2+0</f>
-        <v/>
-      </c>
-      <c r="B29" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>13</v>
-      </c>
+        <f>IF($B$2="","",$B$2+0)</f>
+        <v/>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5">
-        <f>$B$2+1</f>
-        <v/>
-      </c>
-      <c r="B30" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="C30" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="D30" s="6" t="n">
-        <v>14</v>
-      </c>
+        <f>IF($B$2="","",$B$2+1)</f>
+        <v/>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5">
-        <f>$B$2+2</f>
-        <v/>
-      </c>
-      <c r="B31" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="C31" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="D31" s="6" t="n">
-        <v>15</v>
-      </c>
+        <f>IF($B$2="","",$B$2+2)</f>
+        <v/>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5">
-        <f>$B$2+3</f>
-        <v/>
-      </c>
-      <c r="B32" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="C32" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="D32" s="6" t="n">
-        <v>15</v>
-      </c>
+        <f>IF($B$2="","",$B$2+3)</f>
+        <v/>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5">
-        <f>$B$2+4</f>
-        <v/>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="C33" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>16</v>
-      </c>
+        <f>IF($B$2="","",$B$2+4)</f>
+        <v/>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5">
-        <f>$B$2+5</f>
-        <v/>
-      </c>
-      <c r="B34" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="C34" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="D34" s="6" t="n">
-        <v>15</v>
-      </c>
+        <f>IF($B$2="","",$B$2+5)</f>
+        <v/>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5">
-        <f>$B$2+6</f>
-        <v/>
-      </c>
-      <c r="B35" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="C35" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="D35" s="6" t="n">
-        <v>14</v>
-      </c>
+        <f>IF($B$2="","",$B$2+6)</f>
+        <v/>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5">
-        <f>$B$2+7</f>
-        <v/>
-      </c>
-      <c r="B36" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="C36" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="D36" s="6" t="n">
-        <v>14</v>
-      </c>
+        <f>IF($B$2="","",$B$2+7)</f>
+        <v/>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5">
-        <f>$B$2+8</f>
-        <v/>
-      </c>
-      <c r="B37" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="C37" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="D37" s="6" t="n">
-        <v>13</v>
-      </c>
+        <f>IF($B$2="","",$B$2+8)</f>
+        <v/>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5">
-        <f>$B$2+9</f>
-        <v/>
-      </c>
-      <c r="B38" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="C38" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="D38" s="6" t="n">
-        <v>13</v>
-      </c>
+        <f>IF($B$2="","",$B$2+9)</f>
+        <v/>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -2868,36 +3882,24 @@
         </is>
       </c>
       <c r="B39" s="11">
-        <f>$B$4</f>
+        <f>IF($B$4="","",$B$4)</f>
         <v/>
       </c>
     </row>
     <row r="40"/>
     <row r="41"/>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>Zanieczyszczenie 3</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>NO2</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>ditlenek azotu</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>µg/m3</t>
-        </is>
-      </c>
-      <c r="E42" s="10" t="inlineStr">
-        <is>
-          <t>Wprowadź 10 kolejnych dni danych</t>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="9" t="n"/>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>Uzupełnij alias, nazwę, jednostkę i 10 kolejnych dni danych</t>
         </is>
       </c>
     </row>
@@ -2925,153 +3927,93 @@
     </row>
     <row r="44">
       <c r="A44" s="5">
-        <f>$B$2+0</f>
-        <v/>
-      </c>
-      <c r="B44" s="6" t="n">
-        <v>88</v>
-      </c>
-      <c r="C44" s="6" t="n">
-        <v>61</v>
-      </c>
-      <c r="D44" s="6" t="n">
-        <v>39</v>
-      </c>
+        <f>IF($B$2="","",$B$2+0)</f>
+        <v/>
+      </c>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5">
-        <f>$B$2+1</f>
-        <v/>
-      </c>
-      <c r="B45" s="6" t="n">
-        <v>92</v>
-      </c>
-      <c r="C45" s="6" t="n">
-        <v>64</v>
-      </c>
-      <c r="D45" s="6" t="n">
-        <v>41</v>
-      </c>
+        <f>IF($B$2="","",$B$2+1)</f>
+        <v/>
+      </c>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5">
-        <f>$B$2+2</f>
-        <v/>
-      </c>
-      <c r="B46" s="6" t="n">
-        <v>96</v>
-      </c>
-      <c r="C46" s="6" t="n">
-        <v>67</v>
-      </c>
-      <c r="D46" s="6" t="n">
-        <v>43</v>
-      </c>
+        <f>IF($B$2="","",$B$2+2)</f>
+        <v/>
+      </c>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5">
-        <f>$B$2+3</f>
-        <v/>
-      </c>
-      <c r="B47" s="6" t="n">
-        <v>101</v>
-      </c>
-      <c r="C47" s="6" t="n">
-        <v>69</v>
-      </c>
-      <c r="D47" s="6" t="n">
-        <v>45</v>
-      </c>
+        <f>IF($B$2="","",$B$2+3)</f>
+        <v/>
+      </c>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5">
-        <f>$B$2+4</f>
-        <v/>
-      </c>
-      <c r="B48" s="6" t="n">
-        <v>98</v>
-      </c>
-      <c r="C48" s="6" t="n">
-        <v>70</v>
-      </c>
-      <c r="D48" s="6" t="n">
-        <v>44</v>
-      </c>
+        <f>IF($B$2="","",$B$2+4)</f>
+        <v/>
+      </c>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5">
-        <f>$B$2+5</f>
-        <v/>
-      </c>
-      <c r="B49" s="6" t="n">
-        <v>95</v>
-      </c>
-      <c r="C49" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="D49" s="6" t="n">
-        <v>42</v>
-      </c>
+        <f>IF($B$2="","",$B$2+5)</f>
+        <v/>
+      </c>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5">
-        <f>$B$2+6</f>
-        <v/>
-      </c>
-      <c r="B50" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="C50" s="6" t="n">
-        <v>65</v>
-      </c>
-      <c r="D50" s="6" t="n">
-        <v>41</v>
-      </c>
+        <f>IF($B$2="","",$B$2+6)</f>
+        <v/>
+      </c>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5">
-        <f>$B$2+7</f>
-        <v/>
-      </c>
-      <c r="B51" s="6" t="n">
-        <v>87</v>
-      </c>
-      <c r="C51" s="6" t="n">
-        <v>63</v>
-      </c>
-      <c r="D51" s="6" t="n">
-        <v>39</v>
-      </c>
+        <f>IF($B$2="","",$B$2+7)</f>
+        <v/>
+      </c>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5">
-        <f>$B$2+8</f>
-        <v/>
-      </c>
-      <c r="B52" s="6" t="n">
-        <v>84</v>
-      </c>
-      <c r="C52" s="6" t="n">
-        <v>61</v>
-      </c>
-      <c r="D52" s="6" t="n">
-        <v>38</v>
-      </c>
+        <f>IF($B$2="","",$B$2+8)</f>
+        <v/>
+      </c>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5">
-        <f>$B$2+9</f>
-        <v/>
-      </c>
-      <c r="B53" s="6" t="n">
-        <v>82</v>
-      </c>
-      <c r="C53" s="6" t="n">
-        <v>59</v>
-      </c>
-      <c r="D53" s="6" t="n">
-        <v>37</v>
-      </c>
+        <f>IF($B$2="","",$B$2+9)</f>
+        <v/>
+      </c>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -3080,36 +4022,24 @@
         </is>
       </c>
       <c r="B54" s="11">
-        <f>$B$4</f>
+        <f>IF($B$4="","",$B$4)</f>
         <v/>
       </c>
     </row>
     <row r="55"/>
     <row r="56"/>
     <row r="57">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>Zanieczyszczenie 4</t>
         </is>
       </c>
-      <c r="B57" s="8" t="inlineStr">
-        <is>
-          <t>PM10</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="inlineStr">
-        <is>
-          <t>pył zawieszony PM10</t>
-        </is>
-      </c>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>µg/m3</t>
-        </is>
-      </c>
-      <c r="E57" s="10" t="inlineStr">
-        <is>
-          <t>Wprowadź 10 kolejnych dni danych</t>
+      <c r="B57" s="9" t="n"/>
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="9" t="n"/>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>Uzupełnij alias, nazwę, jednostkę i 10 kolejnych dni danych</t>
         </is>
       </c>
     </row>
@@ -3137,153 +4067,93 @@
     </row>
     <row r="59">
       <c r="A59" s="5">
-        <f>$B$2+0</f>
-        <v/>
-      </c>
-      <c r="B59" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="C59" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="D59" s="6" t="n">
-        <v>18</v>
-      </c>
+        <f>IF($B$2="","",$B$2+0)</f>
+        <v/>
+      </c>
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5">
-        <f>$B$2+1</f>
-        <v/>
-      </c>
-      <c r="B60" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="C60" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="D60" s="6" t="n">
-        <v>19</v>
-      </c>
+        <f>IF($B$2="","",$B$2+1)</f>
+        <v/>
+      </c>
+      <c r="B60" s="6" t="n"/>
+      <c r="C60" s="6" t="n"/>
+      <c r="D60" s="6" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5">
-        <f>$B$2+2</f>
-        <v/>
-      </c>
-      <c r="B61" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="C61" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="D61" s="6" t="n">
-        <v>21</v>
-      </c>
+        <f>IF($B$2="","",$B$2+2)</f>
+        <v/>
+      </c>
+      <c r="B61" s="6" t="n"/>
+      <c r="C61" s="6" t="n"/>
+      <c r="D61" s="6" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5">
-        <f>$B$2+3</f>
-        <v/>
-      </c>
-      <c r="B62" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="C62" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="D62" s="6" t="n">
-        <v>22</v>
-      </c>
+        <f>IF($B$2="","",$B$2+3)</f>
+        <v/>
+      </c>
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5">
-        <f>$B$2+4</f>
-        <v/>
-      </c>
-      <c r="B63" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="C63" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="D63" s="6" t="n">
-        <v>21</v>
-      </c>
+        <f>IF($B$2="","",$B$2+4)</f>
+        <v/>
+      </c>
+      <c r="B63" s="6" t="n"/>
+      <c r="C63" s="6" t="n"/>
+      <c r="D63" s="6" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5">
-        <f>$B$2+5</f>
-        <v/>
-      </c>
-      <c r="B64" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="C64" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="D64" s="6" t="n">
-        <v>20</v>
-      </c>
+        <f>IF($B$2="","",$B$2+5)</f>
+        <v/>
+      </c>
+      <c r="B64" s="6" t="n"/>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5">
-        <f>$B$2+6</f>
-        <v/>
-      </c>
-      <c r="B65" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="C65" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="D65" s="6" t="n">
-        <v>19</v>
-      </c>
+        <f>IF($B$2="","",$B$2+6)</f>
+        <v/>
+      </c>
+      <c r="B65" s="6" t="n"/>
+      <c r="C65" s="6" t="n"/>
+      <c r="D65" s="6" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5">
-        <f>$B$2+7</f>
-        <v/>
-      </c>
-      <c r="B66" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="C66" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="D66" s="6" t="n">
-        <v>18</v>
-      </c>
+        <f>IF($B$2="","",$B$2+7)</f>
+        <v/>
+      </c>
+      <c r="B66" s="6" t="n"/>
+      <c r="C66" s="6" t="n"/>
+      <c r="D66" s="6" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5">
-        <f>$B$2+8</f>
-        <v/>
-      </c>
-      <c r="B67" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="C67" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="D67" s="6" t="n">
-        <v>17</v>
-      </c>
+        <f>IF($B$2="","",$B$2+8)</f>
+        <v/>
+      </c>
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="6" t="n"/>
+      <c r="D67" s="6" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="5">
-        <f>$B$2+9</f>
-        <v/>
-      </c>
-      <c r="B68" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="C68" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="D68" s="6" t="n">
-        <v>17</v>
-      </c>
+        <f>IF($B$2="","",$B$2+9)</f>
+        <v/>
+      </c>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="6" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -3292,36 +4162,24 @@
         </is>
       </c>
       <c r="B69" s="11">
-        <f>$B$4</f>
+        <f>IF($B$4="","",$B$4)</f>
         <v/>
       </c>
     </row>
     <row r="70"/>
     <row r="71"/>
     <row r="72">
-      <c r="A72" s="9" t="inlineStr">
+      <c r="A72" s="10" t="inlineStr">
         <is>
           <t>Zanieczyszczenie 5</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="inlineStr">
-        <is>
-          <t>tlenek węgla</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>µg/m3</t>
-        </is>
-      </c>
-      <c r="E72" s="10" t="inlineStr">
-        <is>
-          <t>Wprowadź 10 kolejnych dni danych</t>
+      <c r="B72" s="9" t="n"/>
+      <c r="C72" s="9" t="n"/>
+      <c r="D72" s="9" t="n"/>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>Uzupełnij alias, nazwę, jednostkę i 10 kolejnych dni danych</t>
         </is>
       </c>
     </row>
@@ -3349,153 +4207,93 @@
     </row>
     <row r="74">
       <c r="A74" s="5">
-        <f>$B$2+0</f>
-        <v/>
-      </c>
-      <c r="B74" s="6" t="n">
-        <v>1600</v>
-      </c>
-      <c r="C74" s="6" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D74" s="6" t="n">
-        <v>900</v>
-      </c>
+        <f>IF($B$2="","",$B$2+0)</f>
+        <v/>
+      </c>
+      <c r="B74" s="6" t="n"/>
+      <c r="C74" s="6" t="n"/>
+      <c r="D74" s="6" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5">
-        <f>$B$2+1</f>
-        <v/>
-      </c>
-      <c r="B75" s="6" t="n">
-        <v>1700</v>
-      </c>
-      <c r="C75" s="6" t="n">
-        <v>1360</v>
-      </c>
-      <c r="D75" s="6" t="n">
-        <v>940</v>
-      </c>
+        <f>IF($B$2="","",$B$2+1)</f>
+        <v/>
+      </c>
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="6" t="n"/>
+      <c r="D75" s="6" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5">
-        <f>$B$2+2</f>
-        <v/>
-      </c>
-      <c r="B76" s="6" t="n">
-        <v>1800</v>
-      </c>
-      <c r="C76" s="6" t="n">
-        <v>1400</v>
-      </c>
-      <c r="D76" s="6" t="n">
-        <v>980</v>
-      </c>
+        <f>IF($B$2="","",$B$2+2)</f>
+        <v/>
+      </c>
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="6" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="5">
-        <f>$B$2+3</f>
-        <v/>
-      </c>
-      <c r="B77" s="6" t="n">
-        <v>1750</v>
-      </c>
-      <c r="C77" s="6" t="n">
-        <v>1380</v>
-      </c>
-      <c r="D77" s="6" t="n">
-        <v>990</v>
-      </c>
+        <f>IF($B$2="","",$B$2+3)</f>
+        <v/>
+      </c>
+      <c r="B77" s="6" t="n"/>
+      <c r="C77" s="6" t="n"/>
+      <c r="D77" s="6" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5">
-        <f>$B$2+4</f>
-        <v/>
-      </c>
-      <c r="B78" s="6" t="n">
-        <v>1690</v>
-      </c>
-      <c r="C78" s="6" t="n">
-        <v>1340</v>
-      </c>
-      <c r="D78" s="6" t="n">
-        <v>960</v>
-      </c>
+        <f>IF($B$2="","",$B$2+4)</f>
+        <v/>
+      </c>
+      <c r="B78" s="6" t="n"/>
+      <c r="C78" s="6" t="n"/>
+      <c r="D78" s="6" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5">
-        <f>$B$2+5</f>
-        <v/>
-      </c>
-      <c r="B79" s="6" t="n">
-        <v>1650</v>
-      </c>
-      <c r="C79" s="6" t="n">
-        <v>1320</v>
-      </c>
-      <c r="D79" s="6" t="n">
-        <v>940</v>
-      </c>
+        <f>IF($B$2="","",$B$2+5)</f>
+        <v/>
+      </c>
+      <c r="B79" s="6" t="n"/>
+      <c r="C79" s="6" t="n"/>
+      <c r="D79" s="6" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="5">
-        <f>$B$2+6</f>
-        <v/>
-      </c>
-      <c r="B80" s="6" t="n">
-        <v>1620</v>
-      </c>
-      <c r="C80" s="6" t="n">
-        <v>1290</v>
-      </c>
-      <c r="D80" s="6" t="n">
-        <v>920</v>
-      </c>
+        <f>IF($B$2="","",$B$2+6)</f>
+        <v/>
+      </c>
+      <c r="B80" s="6" t="n"/>
+      <c r="C80" s="6" t="n"/>
+      <c r="D80" s="6" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="5">
-        <f>$B$2+7</f>
-        <v/>
-      </c>
-      <c r="B81" s="6" t="n">
-        <v>1580</v>
-      </c>
-      <c r="C81" s="6" t="n">
-        <v>1260</v>
-      </c>
-      <c r="D81" s="6" t="n">
-        <v>900</v>
-      </c>
+        <f>IF($B$2="","",$B$2+7)</f>
+        <v/>
+      </c>
+      <c r="B81" s="6" t="n"/>
+      <c r="C81" s="6" t="n"/>
+      <c r="D81" s="6" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5">
-        <f>$B$2+8</f>
-        <v/>
-      </c>
-      <c r="B82" s="6" t="n">
-        <v>1540</v>
-      </c>
-      <c r="C82" s="6" t="n">
-        <v>1230</v>
-      </c>
-      <c r="D82" s="6" t="n">
-        <v>880</v>
-      </c>
+        <f>IF($B$2="","",$B$2+8)</f>
+        <v/>
+      </c>
+      <c r="B82" s="6" t="n"/>
+      <c r="C82" s="6" t="n"/>
+      <c r="D82" s="6" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5">
-        <f>$B$2+9</f>
-        <v/>
-      </c>
-      <c r="B83" s="6" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C83" s="6" t="n">
-        <v>1210</v>
-      </c>
-      <c r="D83" s="6" t="n">
-        <v>860</v>
-      </c>
+        <f>IF($B$2="","",$B$2+9)</f>
+        <v/>
+      </c>
+      <c r="B83" s="6" t="n"/>
+      <c r="C83" s="6" t="n"/>
+      <c r="D83" s="6" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -3504,36 +4302,24 @@
         </is>
       </c>
       <c r="B84" s="11">
-        <f>$B$4</f>
+        <f>IF($B$4="","",$B$4)</f>
         <v/>
       </c>
     </row>
     <row r="85"/>
     <row r="86"/>
     <row r="87">
-      <c r="A87" s="9" t="inlineStr">
+      <c r="A87" s="10" t="inlineStr">
         <is>
           <t>Zanieczyszczenie 6</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>BENZEN</t>
-        </is>
-      </c>
-      <c r="C87" s="8" t="inlineStr">
-        <is>
-          <t>benzen</t>
-        </is>
-      </c>
-      <c r="D87" s="8" t="inlineStr">
-        <is>
-          <t>µg/m3</t>
-        </is>
-      </c>
-      <c r="E87" s="10" t="inlineStr">
-        <is>
-          <t>Wprowadź 10 kolejnych dni danych</t>
+      <c r="B87" s="9" t="n"/>
+      <c r="C87" s="9" t="n"/>
+      <c r="D87" s="9" t="n"/>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>Uzupełnij alias, nazwę, jednostkę i 10 kolejnych dni danych</t>
         </is>
       </c>
     </row>
@@ -3561,153 +4347,93 @@
     </row>
     <row r="89">
       <c r="A89" s="5">
-        <f>$B$2+0</f>
-        <v/>
-      </c>
-      <c r="B89" s="6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C89" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D89" s="6" t="n">
-        <v>0.5</v>
-      </c>
+        <f>IF($B$2="","",$B$2+0)</f>
+        <v/>
+      </c>
+      <c r="B89" s="6" t="n"/>
+      <c r="C89" s="6" t="n"/>
+      <c r="D89" s="6" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="5">
-        <f>$B$2+1</f>
-        <v/>
-      </c>
-      <c r="B90" s="6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C90" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D90" s="6" t="n">
-        <v>0.6</v>
-      </c>
+        <f>IF($B$2="","",$B$2+1)</f>
+        <v/>
+      </c>
+      <c r="B90" s="6" t="n"/>
+      <c r="C90" s="6" t="n"/>
+      <c r="D90" s="6" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="5">
-        <f>$B$2+2</f>
-        <v/>
-      </c>
-      <c r="B91" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C91" s="6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D91" s="6" t="n">
-        <v>0.7</v>
-      </c>
+        <f>IF($B$2="","",$B$2+2)</f>
+        <v/>
+      </c>
+      <c r="B91" s="6" t="n"/>
+      <c r="C91" s="6" t="n"/>
+      <c r="D91" s="6" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="5">
-        <f>$B$2+3</f>
-        <v/>
-      </c>
-      <c r="B92" s="6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C92" s="6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D92" s="6" t="n">
-        <v>0.8</v>
-      </c>
+        <f>IF($B$2="","",$B$2+3)</f>
+        <v/>
+      </c>
+      <c r="B92" s="6" t="n"/>
+      <c r="C92" s="6" t="n"/>
+      <c r="D92" s="6" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="5">
-        <f>$B$2+4</f>
-        <v/>
-      </c>
-      <c r="B93" s="6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C93" s="6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D93" s="6" t="n">
-        <v>0.8</v>
-      </c>
+        <f>IF($B$2="","",$B$2+4)</f>
+        <v/>
+      </c>
+      <c r="B93" s="6" t="n"/>
+      <c r="C93" s="6" t="n"/>
+      <c r="D93" s="6" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="5">
-        <f>$B$2+5</f>
-        <v/>
-      </c>
-      <c r="B94" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C94" s="6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D94" s="6" t="n">
-        <v>0.7</v>
-      </c>
+        <f>IF($B$2="","",$B$2+5)</f>
+        <v/>
+      </c>
+      <c r="B94" s="6" t="n"/>
+      <c r="C94" s="6" t="n"/>
+      <c r="D94" s="6" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="5">
-        <f>$B$2+6</f>
-        <v/>
-      </c>
-      <c r="B95" s="6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="C95" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D95" s="6" t="n">
-        <v>0.6</v>
-      </c>
+        <f>IF($B$2="","",$B$2+6)</f>
+        <v/>
+      </c>
+      <c r="B95" s="6" t="n"/>
+      <c r="C95" s="6" t="n"/>
+      <c r="D95" s="6" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="5">
-        <f>$B$2+7</f>
-        <v/>
-      </c>
-      <c r="B96" s="6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C96" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D96" s="6" t="n">
-        <v>0.6</v>
-      </c>
+        <f>IF($B$2="","",$B$2+7)</f>
+        <v/>
+      </c>
+      <c r="B96" s="6" t="n"/>
+      <c r="C96" s="6" t="n"/>
+      <c r="D96" s="6" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="5">
-        <f>$B$2+8</f>
-        <v/>
-      </c>
-      <c r="B97" s="6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="C97" s="6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D97" s="6" t="n">
-        <v>0.5</v>
-      </c>
+        <f>IF($B$2="","",$B$2+8)</f>
+        <v/>
+      </c>
+      <c r="B97" s="6" t="n"/>
+      <c r="C97" s="6" t="n"/>
+      <c r="D97" s="6" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="5">
-        <f>$B$2+9</f>
-        <v/>
-      </c>
-      <c r="B98" s="6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="C98" s="6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D98" s="6" t="n">
-        <v>0.5</v>
-      </c>
+        <f>IF($B$2="","",$B$2+9)</f>
+        <v/>
+      </c>
+      <c r="B98" s="6" t="n"/>
+      <c r="C98" s="6" t="n"/>
+      <c r="D98" s="6" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
@@ -3716,7 +4442,7 @@
         </is>
       </c>
       <c r="B99" s="11">
-        <f>$B$4</f>
+        <f>IF($B$4="","",$B$4)</f>
         <v/>
       </c>
     </row>
@@ -4353,13 +5079,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>miejska</t>
         </is>
       </c>
       <c r="B3" s="12">
-        <f>SUMIF($B$10:$B$27,A3,$O$10:$O$27)</f>
+        <f>IF(SUMPRODUCT(($B$10:$B$27=A3)*(ISNUMBER($K$10:$K$27)))=0,"",SUMIF($B$10:$B$27,A3,$O$10:$O$27))</f>
         <v/>
       </c>
       <c r="C3" s="12">
@@ -4367,7 +5093,7 @@
         <v/>
       </c>
       <c r="D3" s="12">
-        <f>SUMIF($B$10:$B$27,A3,$P$10:$P$27)</f>
+        <f>IF(SUMPRODUCT(($B$10:$B$27=A3)*(ISNUMBER($K$10:$K$27)))=0,"",SUMIF($B$10:$B$27,A3,$P$10:$P$27))</f>
         <v/>
       </c>
       <c r="E3" s="12">
@@ -4392,13 +5118,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>podmiejska</t>
         </is>
       </c>
       <c r="B4" s="12">
-        <f>SUMIF($B$10:$B$27,A4,$O$10:$O$27)</f>
+        <f>IF(SUMPRODUCT(($B$10:$B$27=A4)*(ISNUMBER($K$10:$K$27)))=0,"",SUMIF($B$10:$B$27,A4,$O$10:$O$27))</f>
         <v/>
       </c>
       <c r="C4" s="12">
@@ -4406,7 +5132,7 @@
         <v/>
       </c>
       <c r="D4" s="12">
-        <f>SUMIF($B$10:$B$27,A4,$P$10:$P$27)</f>
+        <f>IF(SUMPRODUCT(($B$10:$B$27=A4)*(ISNUMBER($K$10:$K$27)))=0,"",SUMIF($B$10:$B$27,A4,$P$10:$P$27))</f>
         <v/>
       </c>
       <c r="E4" s="12">
@@ -4431,13 +5157,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>pozamiejska</t>
         </is>
       </c>
       <c r="B5" s="12">
-        <f>SUMIF($B$10:$B$27,A5,$O$10:$O$27)</f>
+        <f>IF(SUMPRODUCT(($B$10:$B$27=A5)*(ISNUMBER($K$10:$K$27)))=0,"",SUMIF($B$10:$B$27,A5,$O$10:$O$27))</f>
         <v/>
       </c>
       <c r="C5" s="12">
@@ -4445,7 +5171,7 @@
         <v/>
       </c>
       <c r="D5" s="12">
-        <f>SUMIF($B$10:$B$27,A5,$P$10:$P$27)</f>
+        <f>IF(SUMPRODUCT(($B$10:$B$27=A5)*(ISNUMBER($K$10:$K$27)))=0,"",SUMIF($B$10:$B$27,A5,$P$10:$P$27))</f>
         <v/>
       </c>
       <c r="E5" s="12">
@@ -4580,10 +5306,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>miejska</t>
         </is>
@@ -4629,11 +5355,11 @@
         <v/>
       </c>
       <c r="M10" s="12">
-        <f>IF(G10="","Brak limitu",IF(K10="","Brak danych",IF(K10&gt;G10,"TAK","NIE")))</f>
+        <f>IF(C10&amp;D10="","",IF(G10="","Brak limitu",IF(K10="","Brak danych",IF(K10&gt;G10,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="N10" s="12">
-        <f>IF(G10="","Brak limitu",IF(L10="","Brak danych",IF(L10&gt;G10,"TAK","NIE")))</f>
+        <f>IF(C10&amp;D10="","",IF(G10="","Brak limitu",IF(L10="","Brak danych",IF(L10&gt;G10,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="O10" s="12">
@@ -4660,17 +5386,16 @@
         <f>SUMIF($B$10:$B$27,B10,$P$10:$P$27)</f>
         <v/>
       </c>
-      <c r="U10" s="12" t="inlineStr">
-        <is>
-          <t>Wskaźnik liczony dla całej stacji</t>
-        </is>
+      <c r="U10" s="12">
+        <f>IF(C10&amp;D10="","","Wskaźnik liczony dla całej stacji")</f>
+        <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>podmiejska</t>
         </is>
@@ -4716,11 +5441,11 @@
         <v/>
       </c>
       <c r="M11" s="12">
-        <f>IF(G11="","Brak limitu",IF(K11="","Brak danych",IF(K11&gt;G11,"TAK","NIE")))</f>
+        <f>IF(C11&amp;D11="","",IF(G11="","Brak limitu",IF(K11="","Brak danych",IF(K11&gt;G11,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="N11" s="12">
-        <f>IF(G11="","Brak limitu",IF(L11="","Brak danych",IF(L11&gt;G11,"TAK","NIE")))</f>
+        <f>IF(C11&amp;D11="","",IF(G11="","Brak limitu",IF(L11="","Brak danych",IF(L11&gt;G11,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="O11" s="12">
@@ -4747,17 +5472,16 @@
         <f>SUMIF($B$10:$B$27,B11,$P$10:$P$27)</f>
         <v/>
       </c>
-      <c r="U11" s="12" t="inlineStr">
-        <is>
-          <t>Wskaźnik liczony dla całej stacji</t>
-        </is>
+      <c r="U11" s="12">
+        <f>IF(C11&amp;D11="","","Wskaźnik liczony dla całej stacji")</f>
+        <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>pozamiejska</t>
         </is>
@@ -4803,11 +5527,11 @@
         <v/>
       </c>
       <c r="M12" s="12">
-        <f>IF(G12="","Brak limitu",IF(K12="","Brak danych",IF(K12&gt;G12,"TAK","NIE")))</f>
+        <f>IF(C12&amp;D12="","",IF(G12="","Brak limitu",IF(K12="","Brak danych",IF(K12&gt;G12,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="N12" s="12">
-        <f>IF(G12="","Brak limitu",IF(L12="","Brak danych",IF(L12&gt;G12,"TAK","NIE")))</f>
+        <f>IF(C12&amp;D12="","",IF(G12="","Brak limitu",IF(L12="","Brak danych",IF(L12&gt;G12,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="O12" s="12">
@@ -4834,17 +5558,16 @@
         <f>SUMIF($B$10:$B$27,B12,$P$10:$P$27)</f>
         <v/>
       </c>
-      <c r="U12" s="12" t="inlineStr">
-        <is>
-          <t>Wskaźnik liczony dla całej stacji</t>
-        </is>
+      <c r="U12" s="12">
+        <f>IF(C12&amp;D12="","","Wskaźnik liczony dla całej stacji")</f>
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="n">
+      <c r="A13" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>miejska</t>
         </is>
@@ -4890,11 +5613,11 @@
         <v/>
       </c>
       <c r="M13" s="12">
-        <f>IF(G13="","Brak limitu",IF(K13="","Brak danych",IF(K13&gt;G13,"TAK","NIE")))</f>
+        <f>IF(C13&amp;D13="","",IF(G13="","Brak limitu",IF(K13="","Brak danych",IF(K13&gt;G13,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="N13" s="12">
-        <f>IF(G13="","Brak limitu",IF(L13="","Brak danych",IF(L13&gt;G13,"TAK","NIE")))</f>
+        <f>IF(C13&amp;D13="","",IF(G13="","Brak limitu",IF(L13="","Brak danych",IF(L13&gt;G13,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="O13" s="12">
@@ -4921,17 +5644,16 @@
         <f>SUMIF($B$10:$B$27,B13,$P$10:$P$27)</f>
         <v/>
       </c>
-      <c r="U13" s="12" t="inlineStr">
-        <is>
-          <t>Wskaźnik liczony dla całej stacji</t>
-        </is>
+      <c r="U13" s="12">
+        <f>IF(C13&amp;D13="","","Wskaźnik liczony dla całej stacji")</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>podmiejska</t>
         </is>
@@ -4977,11 +5699,11 @@
         <v/>
       </c>
       <c r="M14" s="12">
-        <f>IF(G14="","Brak limitu",IF(K14="","Brak danych",IF(K14&gt;G14,"TAK","NIE")))</f>
+        <f>IF(C14&amp;D14="","",IF(G14="","Brak limitu",IF(K14="","Brak danych",IF(K14&gt;G14,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="N14" s="12">
-        <f>IF(G14="","Brak limitu",IF(L14="","Brak danych",IF(L14&gt;G14,"TAK","NIE")))</f>
+        <f>IF(C14&amp;D14="","",IF(G14="","Brak limitu",IF(L14="","Brak danych",IF(L14&gt;G14,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="O14" s="12">
@@ -5008,17 +5730,16 @@
         <f>SUMIF($B$10:$B$27,B14,$P$10:$P$27)</f>
         <v/>
       </c>
-      <c r="U14" s="12" t="inlineStr">
-        <is>
-          <t>Wskaźnik liczony dla całej stacji</t>
-        </is>
+      <c r="U14" s="12">
+        <f>IF(C14&amp;D14="","","Wskaźnik liczony dla całej stacji")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n">
+      <c r="A15" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>pozamiejska</t>
         </is>
@@ -5064,11 +5785,11 @@
         <v/>
       </c>
       <c r="M15" s="12">
-        <f>IF(G15="","Brak limitu",IF(K15="","Brak danych",IF(K15&gt;G15,"TAK","NIE")))</f>
+        <f>IF(C15&amp;D15="","",IF(G15="","Brak limitu",IF(K15="","Brak danych",IF(K15&gt;G15,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="N15" s="12">
-        <f>IF(G15="","Brak limitu",IF(L15="","Brak danych",IF(L15&gt;G15,"TAK","NIE")))</f>
+        <f>IF(C15&amp;D15="","",IF(G15="","Brak limitu",IF(L15="","Brak danych",IF(L15&gt;G15,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="O15" s="12">
@@ -5095,17 +5816,16 @@
         <f>SUMIF($B$10:$B$27,B15,$P$10:$P$27)</f>
         <v/>
       </c>
-      <c r="U15" s="12" t="inlineStr">
-        <is>
-          <t>Wskaźnik liczony dla całej stacji</t>
-        </is>
+      <c r="U15" s="12">
+        <f>IF(C15&amp;D15="","","Wskaźnik liczony dla całej stacji")</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>miejska</t>
         </is>
@@ -5151,11 +5871,11 @@
         <v/>
       </c>
       <c r="M16" s="12">
-        <f>IF(G16="","Brak limitu",IF(K16="","Brak danych",IF(K16&gt;G16,"TAK","NIE")))</f>
+        <f>IF(C16&amp;D16="","",IF(G16="","Brak limitu",IF(K16="","Brak danych",IF(K16&gt;G16,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="N16" s="12">
-        <f>IF(G16="","Brak limitu",IF(L16="","Brak danych",IF(L16&gt;G16,"TAK","NIE")))</f>
+        <f>IF(C16&amp;D16="","",IF(G16="","Brak limitu",IF(L16="","Brak danych",IF(L16&gt;G16,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="O16" s="12">
@@ -5182,17 +5902,16 @@
         <f>SUMIF($B$10:$B$27,B16,$P$10:$P$27)</f>
         <v/>
       </c>
-      <c r="U16" s="12" t="inlineStr">
-        <is>
-          <t>Wskaźnik liczony dla całej stacji</t>
-        </is>
+      <c r="U16" s="12">
+        <f>IF(C16&amp;D16="","","Wskaźnik liczony dla całej stacji")</f>
+        <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n">
+      <c r="A17" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>podmiejska</t>
         </is>
@@ -5238,11 +5957,11 @@
         <v/>
       </c>
       <c r="M17" s="12">
-        <f>IF(G17="","Brak limitu",IF(K17="","Brak danych",IF(K17&gt;G17,"TAK","NIE")))</f>
+        <f>IF(C17&amp;D17="","",IF(G17="","Brak limitu",IF(K17="","Brak danych",IF(K17&gt;G17,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="N17" s="12">
-        <f>IF(G17="","Brak limitu",IF(L17="","Brak danych",IF(L17&gt;G17,"TAK","NIE")))</f>
+        <f>IF(C17&amp;D17="","",IF(G17="","Brak limitu",IF(L17="","Brak danych",IF(L17&gt;G17,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="O17" s="12">
@@ -5269,17 +5988,16 @@
         <f>SUMIF($B$10:$B$27,B17,$P$10:$P$27)</f>
         <v/>
       </c>
-      <c r="U17" s="12" t="inlineStr">
-        <is>
-          <t>Wskaźnik liczony dla całej stacji</t>
-        </is>
+      <c r="U17" s="12">
+        <f>IF(C17&amp;D17="","","Wskaźnik liczony dla całej stacji")</f>
+        <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n">
+      <c r="A18" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>pozamiejska</t>
         </is>
@@ -5325,11 +6043,11 @@
         <v/>
       </c>
       <c r="M18" s="12">
-        <f>IF(G18="","Brak limitu",IF(K18="","Brak danych",IF(K18&gt;G18,"TAK","NIE")))</f>
+        <f>IF(C18&amp;D18="","",IF(G18="","Brak limitu",IF(K18="","Brak danych",IF(K18&gt;G18,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="N18" s="12">
-        <f>IF(G18="","Brak limitu",IF(L18="","Brak danych",IF(L18&gt;G18,"TAK","NIE")))</f>
+        <f>IF(C18&amp;D18="","",IF(G18="","Brak limitu",IF(L18="","Brak danych",IF(L18&gt;G18,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="O18" s="12">
@@ -5356,17 +6074,16 @@
         <f>SUMIF($B$10:$B$27,B18,$P$10:$P$27)</f>
         <v/>
       </c>
-      <c r="U18" s="12" t="inlineStr">
-        <is>
-          <t>Wskaźnik liczony dla całej stacji</t>
-        </is>
+      <c r="U18" s="12">
+        <f>IF(C18&amp;D18="","","Wskaźnik liczony dla całej stacji")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n">
+      <c r="A19" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>miejska</t>
         </is>
@@ -5412,11 +6129,11 @@
         <v/>
       </c>
       <c r="M19" s="12">
-        <f>IF(G19="","Brak limitu",IF(K19="","Brak danych",IF(K19&gt;G19,"TAK","NIE")))</f>
+        <f>IF(C19&amp;D19="","",IF(G19="","Brak limitu",IF(K19="","Brak danych",IF(K19&gt;G19,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="N19" s="12">
-        <f>IF(G19="","Brak limitu",IF(L19="","Brak danych",IF(L19&gt;G19,"TAK","NIE")))</f>
+        <f>IF(C19&amp;D19="","",IF(G19="","Brak limitu",IF(L19="","Brak danych",IF(L19&gt;G19,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="O19" s="12">
@@ -5443,17 +6160,16 @@
         <f>SUMIF($B$10:$B$27,B19,$P$10:$P$27)</f>
         <v/>
       </c>
-      <c r="U19" s="12" t="inlineStr">
-        <is>
-          <t>Wskaźnik liczony dla całej stacji</t>
-        </is>
+      <c r="U19" s="12">
+        <f>IF(C19&amp;D19="","","Wskaźnik liczony dla całej stacji")</f>
+        <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>podmiejska</t>
         </is>
@@ -5499,11 +6215,11 @@
         <v/>
       </c>
       <c r="M20" s="12">
-        <f>IF(G20="","Brak limitu",IF(K20="","Brak danych",IF(K20&gt;G20,"TAK","NIE")))</f>
+        <f>IF(C20&amp;D20="","",IF(G20="","Brak limitu",IF(K20="","Brak danych",IF(K20&gt;G20,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="N20" s="12">
-        <f>IF(G20="","Brak limitu",IF(L20="","Brak danych",IF(L20&gt;G20,"TAK","NIE")))</f>
+        <f>IF(C20&amp;D20="","",IF(G20="","Brak limitu",IF(L20="","Brak danych",IF(L20&gt;G20,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="O20" s="12">
@@ -5530,17 +6246,16 @@
         <f>SUMIF($B$10:$B$27,B20,$P$10:$P$27)</f>
         <v/>
       </c>
-      <c r="U20" s="12" t="inlineStr">
-        <is>
-          <t>Wskaźnik liczony dla całej stacji</t>
-        </is>
+      <c r="U20" s="12">
+        <f>IF(C20&amp;D20="","","Wskaźnik liczony dla całej stacji")</f>
+        <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="n">
+      <c r="A21" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>pozamiejska</t>
         </is>
@@ -5586,11 +6301,11 @@
         <v/>
       </c>
       <c r="M21" s="12">
-        <f>IF(G21="","Brak limitu",IF(K21="","Brak danych",IF(K21&gt;G21,"TAK","NIE")))</f>
+        <f>IF(C21&amp;D21="","",IF(G21="","Brak limitu",IF(K21="","Brak danych",IF(K21&gt;G21,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="N21" s="12">
-        <f>IF(G21="","Brak limitu",IF(L21="","Brak danych",IF(L21&gt;G21,"TAK","NIE")))</f>
+        <f>IF(C21&amp;D21="","",IF(G21="","Brak limitu",IF(L21="","Brak danych",IF(L21&gt;G21,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="O21" s="12">
@@ -5617,17 +6332,16 @@
         <f>SUMIF($B$10:$B$27,B21,$P$10:$P$27)</f>
         <v/>
       </c>
-      <c r="U21" s="12" t="inlineStr">
-        <is>
-          <t>Wskaźnik liczony dla całej stacji</t>
-        </is>
+      <c r="U21" s="12">
+        <f>IF(C21&amp;D21="","","Wskaźnik liczony dla całej stacji")</f>
+        <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>miejska</t>
         </is>
@@ -5673,11 +6387,11 @@
         <v/>
       </c>
       <c r="M22" s="12">
-        <f>IF(G22="","Brak limitu",IF(K22="","Brak danych",IF(K22&gt;G22,"TAK","NIE")))</f>
+        <f>IF(C22&amp;D22="","",IF(G22="","Brak limitu",IF(K22="","Brak danych",IF(K22&gt;G22,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="N22" s="12">
-        <f>IF(G22="","Brak limitu",IF(L22="","Brak danych",IF(L22&gt;G22,"TAK","NIE")))</f>
+        <f>IF(C22&amp;D22="","",IF(G22="","Brak limitu",IF(L22="","Brak danych",IF(L22&gt;G22,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="O22" s="12">
@@ -5704,17 +6418,16 @@
         <f>SUMIF($B$10:$B$27,B22,$P$10:$P$27)</f>
         <v/>
       </c>
-      <c r="U22" s="12" t="inlineStr">
-        <is>
-          <t>Wskaźnik liczony dla całej stacji</t>
-        </is>
+      <c r="U22" s="12">
+        <f>IF(C22&amp;D22="","","Wskaźnik liczony dla całej stacji")</f>
+        <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n">
+      <c r="A23" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>podmiejska</t>
         </is>
@@ -5760,11 +6473,11 @@
         <v/>
       </c>
       <c r="M23" s="12">
-        <f>IF(G23="","Brak limitu",IF(K23="","Brak danych",IF(K23&gt;G23,"TAK","NIE")))</f>
+        <f>IF(C23&amp;D23="","",IF(G23="","Brak limitu",IF(K23="","Brak danych",IF(K23&gt;G23,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="N23" s="12">
-        <f>IF(G23="","Brak limitu",IF(L23="","Brak danych",IF(L23&gt;G23,"TAK","NIE")))</f>
+        <f>IF(C23&amp;D23="","",IF(G23="","Brak limitu",IF(L23="","Brak danych",IF(L23&gt;G23,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="O23" s="12">
@@ -5791,17 +6504,16 @@
         <f>SUMIF($B$10:$B$27,B23,$P$10:$P$27)</f>
         <v/>
       </c>
-      <c r="U23" s="12" t="inlineStr">
-        <is>
-          <t>Wskaźnik liczony dla całej stacji</t>
-        </is>
+      <c r="U23" s="12">
+        <f>IF(C23&amp;D23="","","Wskaźnik liczony dla całej stacji")</f>
+        <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n">
+      <c r="A24" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>pozamiejska</t>
         </is>
@@ -5847,11 +6559,11 @@
         <v/>
       </c>
       <c r="M24" s="12">
-        <f>IF(G24="","Brak limitu",IF(K24="","Brak danych",IF(K24&gt;G24,"TAK","NIE")))</f>
+        <f>IF(C24&amp;D24="","",IF(G24="","Brak limitu",IF(K24="","Brak danych",IF(K24&gt;G24,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="N24" s="12">
-        <f>IF(G24="","Brak limitu",IF(L24="","Brak danych",IF(L24&gt;G24,"TAK","NIE")))</f>
+        <f>IF(C24&amp;D24="","",IF(G24="","Brak limitu",IF(L24="","Brak danych",IF(L24&gt;G24,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="O24" s="12">
@@ -5878,17 +6590,16 @@
         <f>SUMIF($B$10:$B$27,B24,$P$10:$P$27)</f>
         <v/>
       </c>
-      <c r="U24" s="12" t="inlineStr">
-        <is>
-          <t>Wskaźnik liczony dla całej stacji</t>
-        </is>
+      <c r="U24" s="12">
+        <f>IF(C24&amp;D24="","","Wskaźnik liczony dla całej stacji")</f>
+        <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="n">
+      <c r="A25" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>miejska</t>
         </is>
@@ -5934,11 +6645,11 @@
         <v/>
       </c>
       <c r="M25" s="12">
-        <f>IF(G25="","Brak limitu",IF(K25="","Brak danych",IF(K25&gt;G25,"TAK","NIE")))</f>
+        <f>IF(C25&amp;D25="","",IF(G25="","Brak limitu",IF(K25="","Brak danych",IF(K25&gt;G25,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="N25" s="12">
-        <f>IF(G25="","Brak limitu",IF(L25="","Brak danych",IF(L25&gt;G25,"TAK","NIE")))</f>
+        <f>IF(C25&amp;D25="","",IF(G25="","Brak limitu",IF(L25="","Brak danych",IF(L25&gt;G25,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="O25" s="12">
@@ -5965,17 +6676,16 @@
         <f>SUMIF($B$10:$B$27,B25,$P$10:$P$27)</f>
         <v/>
       </c>
-      <c r="U25" s="12" t="inlineStr">
-        <is>
-          <t>Wskaźnik liczony dla całej stacji</t>
-        </is>
+      <c r="U25" s="12">
+        <f>IF(C25&amp;D25="","","Wskaźnik liczony dla całej stacji")</f>
+        <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>podmiejska</t>
         </is>
@@ -6021,11 +6731,11 @@
         <v/>
       </c>
       <c r="M26" s="12">
-        <f>IF(G26="","Brak limitu",IF(K26="","Brak danych",IF(K26&gt;G26,"TAK","NIE")))</f>
+        <f>IF(C26&amp;D26="","",IF(G26="","Brak limitu",IF(K26="","Brak danych",IF(K26&gt;G26,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="N26" s="12">
-        <f>IF(G26="","Brak limitu",IF(L26="","Brak danych",IF(L26&gt;G26,"TAK","NIE")))</f>
+        <f>IF(C26&amp;D26="","",IF(G26="","Brak limitu",IF(L26="","Brak danych",IF(L26&gt;G26,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="O26" s="12">
@@ -6052,17 +6762,16 @@
         <f>SUMIF($B$10:$B$27,B26,$P$10:$P$27)</f>
         <v/>
       </c>
-      <c r="U26" s="12" t="inlineStr">
-        <is>
-          <t>Wskaźnik liczony dla całej stacji</t>
-        </is>
+      <c r="U26" s="12">
+        <f>IF(C26&amp;D26="","","Wskaźnik liczony dla całej stacji")</f>
+        <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="n">
+      <c r="A27" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>pozamiejska</t>
         </is>
@@ -6108,11 +6817,11 @@
         <v/>
       </c>
       <c r="M27" s="12">
-        <f>IF(G27="","Brak limitu",IF(K27="","Brak danych",IF(K27&gt;G27,"TAK","NIE")))</f>
+        <f>IF(C27&amp;D27="","",IF(G27="","Brak limitu",IF(K27="","Brak danych",IF(K27&gt;G27,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="N27" s="12">
-        <f>IF(G27="","Brak limitu",IF(L27="","Brak danych",IF(L27&gt;G27,"TAK","NIE")))</f>
+        <f>IF(C27&amp;D27="","",IF(G27="","Brak limitu",IF(L27="","Brak danych",IF(L27&gt;G27,"TAK","NIE"))))</f>
         <v/>
       </c>
       <c r="O27" s="12">
@@ -6139,10 +6848,9 @@
         <f>SUMIF($B$10:$B$27,B27,$P$10:$P$27)</f>
         <v/>
       </c>
-      <c r="U27" s="12" t="inlineStr">
-        <is>
-          <t>Wskaźnik liczony dla całej stacji</t>
-        </is>
+      <c r="U27" s="12">
+        <f>IF(C27&amp;D27="","","Wskaźnik liczony dla całej stacji")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -6159,7 +6867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6174,6 +6882,7 @@
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
+    <col hidden="1" width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6186,8 +6895,42 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>Wykresy korzystają bezpośrednio z danych z arkusza Powietrze_Dane.</t>
-        </is>
+          <t>Wykresy korzystają bezpośrednio z danych z arkusza Powietrze_Dane i pozostają widoczne także przy pustych danych wejściowych.</t>
+        </is>
+      </c>
+      <c r="N2" s="11">
+        <f>IF(AND(Powietrze_Dane!$C$12&lt;&gt;"",Powietrze_Dane!$D$12&lt;&gt;""),Powietrze_Dane!$C$12&amp;" ["&amp;Powietrze_Dane!$D$12&amp;"]","Zanieczyszczenie 1 [jednostka]")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="N3" s="11">
+        <f>IF(AND(Powietrze_Dane!$C$27&lt;&gt;"",Powietrze_Dane!$D$27&lt;&gt;""),Powietrze_Dane!$C$27&amp;" ["&amp;Powietrze_Dane!$D$27&amp;"]","Zanieczyszczenie 2 [jednostka]")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="N4" s="11">
+        <f>IF(AND(Powietrze_Dane!$C$42&lt;&gt;"",Powietrze_Dane!$D$42&lt;&gt;""),Powietrze_Dane!$C$42&amp;" ["&amp;Powietrze_Dane!$D$42&amp;"]","Zanieczyszczenie 3 [jednostka]")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="N5" s="11">
+        <f>IF(AND(Powietrze_Dane!$C$57&lt;&gt;"",Powietrze_Dane!$D$57&lt;&gt;""),Powietrze_Dane!$C$57&amp;" ["&amp;Powietrze_Dane!$D$57&amp;"]","Zanieczyszczenie 4 [jednostka]")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="N6" s="11">
+        <f>IF(AND(Powietrze_Dane!$C$72&lt;&gt;"",Powietrze_Dane!$D$72&lt;&gt;""),Powietrze_Dane!$C$72&amp;" ["&amp;Powietrze_Dane!$D$72&amp;"]","Zanieczyszczenie 5 [jednostka]")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="N7" s="11">
+        <f>IF(AND(Powietrze_Dane!$C$87&lt;&gt;"",Powietrze_Dane!$D$87&lt;&gt;""),Powietrze_Dane!$C$87&amp;" ["&amp;Powietrze_Dane!$D$87&amp;"]","Zanieczyszczenie 6 [jednostka]")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -6200,6 +6943,994 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" min="32" max="32"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ćwiczenie nr 1 - Poziom zanieczyszczenia powietrza</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="Z2" s="11">
+        <f>Powietrze_Dane!$B$12</f>
+        <v/>
+      </c>
+      <c r="AA2" s="11">
+        <f>Powietrze_Dane!$C$12</f>
+        <v/>
+      </c>
+      <c r="AB2" s="11">
+        <f>Powietrze_Dane!$D$12</f>
+        <v/>
+      </c>
+      <c r="AC2" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Rok akademicki</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="n"/>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Grupa</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="n"/>
+      <c r="Z3" s="11">
+        <f>Powietrze_Dane!$B$27</f>
+        <v/>
+      </c>
+      <c r="AA3" s="11">
+        <f>Powietrze_Dane!$C$27</f>
+        <v/>
+      </c>
+      <c r="AB3" s="11">
+        <f>Powietrze_Dane!$D$27</f>
+        <v/>
+      </c>
+      <c r="AC3" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Zespół</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Zaliczenie</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="n"/>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Uwagi organizacyjne</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="n"/>
+      <c r="Z4" s="11">
+        <f>Powietrze_Dane!$B$42</f>
+        <v/>
+      </c>
+      <c r="AA4" s="11">
+        <f>Powietrze_Dane!$C$42</f>
+        <v/>
+      </c>
+      <c r="AB4" s="11">
+        <f>Powietrze_Dane!$D$42</f>
+        <v/>
+      </c>
+      <c r="AC4" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="Z5" s="11">
+        <f>Powietrze_Dane!$B$57</f>
+        <v/>
+      </c>
+      <c r="AA5" s="11">
+        <f>Powietrze_Dane!$C$57</f>
+        <v/>
+      </c>
+      <c r="AB5" s="11">
+        <f>Powietrze_Dane!$D$57</f>
+        <v/>
+      </c>
+      <c r="AC5" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Skład zespołu badawczego</t>
+        </is>
+      </c>
+      <c r="Z6" s="11">
+        <f>Powietrze_Dane!$B$72</f>
+        <v/>
+      </c>
+      <c r="AA6" s="11">
+        <f>Powietrze_Dane!$C$72</f>
+        <v/>
+      </c>
+      <c r="AB6" s="11">
+        <f>Powietrze_Dane!$D$72</f>
+        <v/>
+      </c>
+      <c r="AC6" s="11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Lp.</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Imię i nazwisko</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Rola w zespole</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Uwagi</t>
+        </is>
+      </c>
+      <c r="Z7" s="11">
+        <f>Powietrze_Dane!$B$87</f>
+        <v/>
+      </c>
+      <c r="AA7" s="11">
+        <f>Powietrze_Dane!$C$87</f>
+        <v/>
+      </c>
+      <c r="AB7" s="11">
+        <f>Powietrze_Dane!$D$87</f>
+        <v/>
+      </c>
+      <c r="AC7" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="AD10" s="11">
+        <f>IFERROR(INDEX($AC$2:$AC$7,AGGREGATE(15,6,(ROW($AC$2:$AC$7)-ROW($AC$2)+1)/((LEN($Z$2:$Z$7)+LEN($AA$2:$AA$7))&gt;0),1)),"")</f>
+        <v/>
+      </c>
+      <c r="AE10" s="11">
+        <f>IF($AD10="","",INDEX($AA$2:$AA$7,$AD10))</f>
+        <v/>
+      </c>
+      <c r="AF10" s="11">
+        <f>IF($AD10="","",INDEX($AB$2:$AB$7,$AD10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="AD11" s="11">
+        <f>IFERROR(INDEX($AC$2:$AC$7,AGGREGATE(15,6,(ROW($AC$2:$AC$7)-ROW($AC$2)+1)/((LEN($Z$2:$Z$7)+LEN($AA$2:$AA$7))&gt;0),2)),"")</f>
+        <v/>
+      </c>
+      <c r="AE11" s="11">
+        <f>IF($AD11="","",INDEX($AA$2:$AA$7,$AD11))</f>
+        <v/>
+      </c>
+      <c r="AF11" s="11">
+        <f>IF($AD11="","",INDEX($AB$2:$AB$7,$AD11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="AD12" s="11">
+        <f>IFERROR(INDEX($AC$2:$AC$7,AGGREGATE(15,6,(ROW($AC$2:$AC$7)-ROW($AC$2)+1)/((LEN($Z$2:$Z$7)+LEN($AA$2:$AA$7))&gt;0),3)),"")</f>
+        <v/>
+      </c>
+      <c r="AE12" s="11">
+        <f>IF($AD12="","",INDEX($AA$2:$AA$7,$AD12))</f>
+        <v/>
+      </c>
+      <c r="AF12" s="11">
+        <f>IF($AD12="","",INDEX($AB$2:$AB$7,$AD12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Wybrane punkty pomiarowe</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Lp.</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Typ punktu</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Województwo</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Adres</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Nazwa stacji</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="15">
+        <f>Powietrze_Dane!$B$7</f>
+        <v/>
+      </c>
+      <c r="C15" s="15">
+        <f>Powietrze_Dane!$C$7</f>
+        <v/>
+      </c>
+      <c r="D15" s="15">
+        <f>Powietrze_Dane!$D$7</f>
+        <v/>
+      </c>
+      <c r="E15" s="15">
+        <f>Powietrze_Dane!$E$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="15">
+        <f>Powietrze_Dane!$B$8</f>
+        <v/>
+      </c>
+      <c r="C16" s="15">
+        <f>Powietrze_Dane!$C$8</f>
+        <v/>
+      </c>
+      <c r="D16" s="15">
+        <f>Powietrze_Dane!$D$8</f>
+        <v/>
+      </c>
+      <c r="E16" s="15">
+        <f>Powietrze_Dane!$E$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" s="15">
+        <f>Powietrze_Dane!$B$9</f>
+        <v/>
+      </c>
+      <c r="C17" s="15">
+        <f>Powietrze_Dane!$C$9</f>
+        <v/>
+      </c>
+      <c r="D17" s="15">
+        <f>Powietrze_Dane!$D$9</f>
+        <v/>
+      </c>
+      <c r="E17" s="15">
+        <f>Powietrze_Dane!$E$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Wybrane zanieczyszczenia</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Lp.</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Nazwa zanieczyszczenia</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Jednostka pomiaru</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Częstotliwość pomiaru</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="15">
+        <f>IF($AE$10="","",$AE$10)</f>
+        <v/>
+      </c>
+      <c r="C21" s="15">
+        <f>IF($AF$10="","",$AF$10)</f>
+        <v/>
+      </c>
+      <c r="D21" s="14" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="15">
+        <f>IF($AE$11="","",$AE$11)</f>
+        <v/>
+      </c>
+      <c r="C22" s="15">
+        <f>IF($AF$11="","",$AF$11)</f>
+        <v/>
+      </c>
+      <c r="D22" s="14" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="15">
+        <f>IF($AE$12="","",$AE$12)</f>
+        <v/>
+      </c>
+      <c r="C23" s="15">
+        <f>IF($AF$12="","",$AF$12)</f>
+        <v/>
+      </c>
+      <c r="D23" s="14" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Zakres dat</t>
+        </is>
+      </c>
+      <c r="B25" s="15">
+        <f>IF(OR(Powietrze_Dane!$B$2="",Powietrze_Dane!$B$3=""),"",TEXT(Powietrze_Dane!$B$2,"dd.mm.yyyy")&amp;" - "&amp;TEXT(Powietrze_Dane!$B$3,"dd.mm.yyyy"))</f>
+        <v/>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Godzina</t>
+        </is>
+      </c>
+      <c r="E25" s="15">
+        <f>IF(Powietrze_Dane!$B$4="","",Powietrze_Dane!$B$4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Tabela parametrów statystycznych danych pomiarowych</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Lp. stacji</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Stacja</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Zanieczyszczenie</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Jednostka</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Średnia</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>MAX</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>Indeks jakości</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>Indeks toksyczności</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>miejska</t>
+        </is>
+      </c>
+      <c r="C29" s="15">
+        <f>IF($AE$10="","",$AE$10)</f>
+        <v/>
+      </c>
+      <c r="D29" s="15">
+        <f>IF($AF$10="","",$AF$10)</f>
+        <v/>
+      </c>
+      <c r="E29" s="15">
+        <f>IF($AD$10="","",INDEX(Powietrze_Wyniki!$J$10:$J$27,($AD$10-1)*3+1))</f>
+        <v/>
+      </c>
+      <c r="F29" s="15">
+        <f>IF($AD$10="","",INDEX(Powietrze_Wyniki!$K$10:$K$27,($AD$10-1)*3+1))</f>
+        <v/>
+      </c>
+      <c r="G29" s="15">
+        <f>IF($AD$10="","",INDEX(Powietrze_Wyniki!$L$10:$L$27,($AD$10-1)*3+1))</f>
+        <v/>
+      </c>
+      <c r="H29" s="15">
+        <f>IF($AE$10="","",Powietrze_Wyniki!$B$3)</f>
+        <v/>
+      </c>
+      <c r="I29" s="15">
+        <f>IF($AE$10="","",Powietrze_Wyniki!$D$3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>miejska</t>
+        </is>
+      </c>
+      <c r="C30" s="15">
+        <f>IF($AE$11="","",$AE$11)</f>
+        <v/>
+      </c>
+      <c r="D30" s="15">
+        <f>IF($AF$11="","",$AF$11)</f>
+        <v/>
+      </c>
+      <c r="E30" s="15">
+        <f>IF($AD$11="","",INDEX(Powietrze_Wyniki!$J$10:$J$27,($AD$11-1)*3+1))</f>
+        <v/>
+      </c>
+      <c r="F30" s="15">
+        <f>IF($AD$11="","",INDEX(Powietrze_Wyniki!$K$10:$K$27,($AD$11-1)*3+1))</f>
+        <v/>
+      </c>
+      <c r="G30" s="15">
+        <f>IF($AD$11="","",INDEX(Powietrze_Wyniki!$L$10:$L$27,($AD$11-1)*3+1))</f>
+        <v/>
+      </c>
+      <c r="H30" s="15">
+        <f>IF($AE$11="","",Powietrze_Wyniki!$B$3)</f>
+        <v/>
+      </c>
+      <c r="I30" s="15">
+        <f>IF($AE$11="","",Powietrze_Wyniki!$D$3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>miejska</t>
+        </is>
+      </c>
+      <c r="C31" s="15">
+        <f>IF($AE$12="","",$AE$12)</f>
+        <v/>
+      </c>
+      <c r="D31" s="15">
+        <f>IF($AF$12="","",$AF$12)</f>
+        <v/>
+      </c>
+      <c r="E31" s="15">
+        <f>IF($AD$12="","",INDEX(Powietrze_Wyniki!$J$10:$J$27,($AD$12-1)*3+1))</f>
+        <v/>
+      </c>
+      <c r="F31" s="15">
+        <f>IF($AD$12="","",INDEX(Powietrze_Wyniki!$K$10:$K$27,($AD$12-1)*3+1))</f>
+        <v/>
+      </c>
+      <c r="G31" s="15">
+        <f>IF($AD$12="","",INDEX(Powietrze_Wyniki!$L$10:$L$27,($AD$12-1)*3+1))</f>
+        <v/>
+      </c>
+      <c r="H31" s="15">
+        <f>IF($AE$12="","",Powietrze_Wyniki!$B$3)</f>
+        <v/>
+      </c>
+      <c r="I31" s="15">
+        <f>IF($AE$12="","",Powietrze_Wyniki!$D$3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>podmiejska</t>
+        </is>
+      </c>
+      <c r="C32" s="15">
+        <f>IF($AE$10="","",$AE$10)</f>
+        <v/>
+      </c>
+      <c r="D32" s="15">
+        <f>IF($AF$10="","",$AF$10)</f>
+        <v/>
+      </c>
+      <c r="E32" s="15">
+        <f>IF($AD$10="","",INDEX(Powietrze_Wyniki!$J$10:$J$27,($AD$10-1)*3+2))</f>
+        <v/>
+      </c>
+      <c r="F32" s="15">
+        <f>IF($AD$10="","",INDEX(Powietrze_Wyniki!$K$10:$K$27,($AD$10-1)*3+2))</f>
+        <v/>
+      </c>
+      <c r="G32" s="15">
+        <f>IF($AD$10="","",INDEX(Powietrze_Wyniki!$L$10:$L$27,($AD$10-1)*3+2))</f>
+        <v/>
+      </c>
+      <c r="H32" s="15">
+        <f>IF($AE$10="","",Powietrze_Wyniki!$B$4)</f>
+        <v/>
+      </c>
+      <c r="I32" s="15">
+        <f>IF($AE$10="","",Powietrze_Wyniki!$D$4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>podmiejska</t>
+        </is>
+      </c>
+      <c r="C33" s="15">
+        <f>IF($AE$11="","",$AE$11)</f>
+        <v/>
+      </c>
+      <c r="D33" s="15">
+        <f>IF($AF$11="","",$AF$11)</f>
+        <v/>
+      </c>
+      <c r="E33" s="15">
+        <f>IF($AD$11="","",INDEX(Powietrze_Wyniki!$J$10:$J$27,($AD$11-1)*3+2))</f>
+        <v/>
+      </c>
+      <c r="F33" s="15">
+        <f>IF($AD$11="","",INDEX(Powietrze_Wyniki!$K$10:$K$27,($AD$11-1)*3+2))</f>
+        <v/>
+      </c>
+      <c r="G33" s="15">
+        <f>IF($AD$11="","",INDEX(Powietrze_Wyniki!$L$10:$L$27,($AD$11-1)*3+2))</f>
+        <v/>
+      </c>
+      <c r="H33" s="15">
+        <f>IF($AE$11="","",Powietrze_Wyniki!$B$4)</f>
+        <v/>
+      </c>
+      <c r="I33" s="15">
+        <f>IF($AE$11="","",Powietrze_Wyniki!$D$4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>podmiejska</t>
+        </is>
+      </c>
+      <c r="C34" s="15">
+        <f>IF($AE$12="","",$AE$12)</f>
+        <v/>
+      </c>
+      <c r="D34" s="15">
+        <f>IF($AF$12="","",$AF$12)</f>
+        <v/>
+      </c>
+      <c r="E34" s="15">
+        <f>IF($AD$12="","",INDEX(Powietrze_Wyniki!$J$10:$J$27,($AD$12-1)*3+2))</f>
+        <v/>
+      </c>
+      <c r="F34" s="15">
+        <f>IF($AD$12="","",INDEX(Powietrze_Wyniki!$K$10:$K$27,($AD$12-1)*3+2))</f>
+        <v/>
+      </c>
+      <c r="G34" s="15">
+        <f>IF($AD$12="","",INDEX(Powietrze_Wyniki!$L$10:$L$27,($AD$12-1)*3+2))</f>
+        <v/>
+      </c>
+      <c r="H34" s="15">
+        <f>IF($AE$12="","",Powietrze_Wyniki!$B$4)</f>
+        <v/>
+      </c>
+      <c r="I34" s="15">
+        <f>IF($AE$12="","",Powietrze_Wyniki!$D$4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>pozamiejska</t>
+        </is>
+      </c>
+      <c r="C35" s="15">
+        <f>IF($AE$10="","",$AE$10)</f>
+        <v/>
+      </c>
+      <c r="D35" s="15">
+        <f>IF($AF$10="","",$AF$10)</f>
+        <v/>
+      </c>
+      <c r="E35" s="15">
+        <f>IF($AD$10="","",INDEX(Powietrze_Wyniki!$J$10:$J$27,($AD$10-1)*3+3))</f>
+        <v/>
+      </c>
+      <c r="F35" s="15">
+        <f>IF($AD$10="","",INDEX(Powietrze_Wyniki!$K$10:$K$27,($AD$10-1)*3+3))</f>
+        <v/>
+      </c>
+      <c r="G35" s="15">
+        <f>IF($AD$10="","",INDEX(Powietrze_Wyniki!$L$10:$L$27,($AD$10-1)*3+3))</f>
+        <v/>
+      </c>
+      <c r="H35" s="15">
+        <f>IF($AE$10="","",Powietrze_Wyniki!$B$5)</f>
+        <v/>
+      </c>
+      <c r="I35" s="15">
+        <f>IF($AE$10="","",Powietrze_Wyniki!$D$5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>pozamiejska</t>
+        </is>
+      </c>
+      <c r="C36" s="15">
+        <f>IF($AE$11="","",$AE$11)</f>
+        <v/>
+      </c>
+      <c r="D36" s="15">
+        <f>IF($AF$11="","",$AF$11)</f>
+        <v/>
+      </c>
+      <c r="E36" s="15">
+        <f>IF($AD$11="","",INDEX(Powietrze_Wyniki!$J$10:$J$27,($AD$11-1)*3+3))</f>
+        <v/>
+      </c>
+      <c r="F36" s="15">
+        <f>IF($AD$11="","",INDEX(Powietrze_Wyniki!$K$10:$K$27,($AD$11-1)*3+3))</f>
+        <v/>
+      </c>
+      <c r="G36" s="15">
+        <f>IF($AD$11="","",INDEX(Powietrze_Wyniki!$L$10:$L$27,($AD$11-1)*3+3))</f>
+        <v/>
+      </c>
+      <c r="H36" s="15">
+        <f>IF($AE$11="","",Powietrze_Wyniki!$B$5)</f>
+        <v/>
+      </c>
+      <c r="I36" s="15">
+        <f>IF($AE$11="","",Powietrze_Wyniki!$D$5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>pozamiejska</t>
+        </is>
+      </c>
+      <c r="C37" s="15">
+        <f>IF($AE$12="","",$AE$12)</f>
+        <v/>
+      </c>
+      <c r="D37" s="15">
+        <f>IF($AF$12="","",$AF$12)</f>
+        <v/>
+      </c>
+      <c r="E37" s="15">
+        <f>IF($AD$12="","",INDEX(Powietrze_Wyniki!$J$10:$J$27,($AD$12-1)*3+3))</f>
+        <v/>
+      </c>
+      <c r="F37" s="15">
+        <f>IF($AD$12="","",INDEX(Powietrze_Wyniki!$K$10:$K$27,($AD$12-1)*3+3))</f>
+        <v/>
+      </c>
+      <c r="G37" s="15">
+        <f>IF($AD$12="","",INDEX(Powietrze_Wyniki!$L$10:$L$27,($AD$12-1)*3+3))</f>
+        <v/>
+      </c>
+      <c r="H37" s="15">
+        <f>IF($AE$12="","",Powietrze_Wyniki!$B$5)</f>
+        <v/>
+      </c>
+      <c r="I37" s="15">
+        <f>IF($AE$12="","",Powietrze_Wyniki!$D$5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Obliczenia</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Stacja</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Psi</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Tau</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Przekroczenia średniej</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>Przekroczenia maksimum</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15">
+        <f>Powietrze_Wyniki!$A$3</f>
+        <v/>
+      </c>
+      <c r="B41" s="15">
+        <f>Powietrze_Wyniki!$B$3</f>
+        <v/>
+      </c>
+      <c r="C41" s="15">
+        <f>Powietrze_Wyniki!$D$3</f>
+        <v/>
+      </c>
+      <c r="D41" s="15">
+        <f>Powietrze_Wyniki!$F$3</f>
+        <v/>
+      </c>
+      <c r="E41" s="15">
+        <f>Powietrze_Wyniki!$G$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15">
+        <f>Powietrze_Wyniki!$A$4</f>
+        <v/>
+      </c>
+      <c r="B42" s="15">
+        <f>Powietrze_Wyniki!$B$4</f>
+        <v/>
+      </c>
+      <c r="C42" s="15">
+        <f>Powietrze_Wyniki!$D$4</f>
+        <v/>
+      </c>
+      <c r="D42" s="15">
+        <f>Powietrze_Wyniki!$F$4</f>
+        <v/>
+      </c>
+      <c r="E42" s="15">
+        <f>Powietrze_Wyniki!$G$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="15">
+        <f>Powietrze_Wyniki!$A$5</f>
+        <v/>
+      </c>
+      <c r="B43" s="15">
+        <f>Powietrze_Wyniki!$B$5</f>
+        <v/>
+      </c>
+      <c r="C43" s="15">
+        <f>Powietrze_Wyniki!$D$5</f>
+        <v/>
+      </c>
+      <c r="D43" s="15">
+        <f>Powietrze_Wyniki!$F$5</f>
+        <v/>
+      </c>
+      <c r="E43" s="15">
+        <f>Powietrze_Wyniki!$G$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Interpretacja wyników</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="n"/>
+    </row>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A46:I50"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="H3:I3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6253,34 +7984,26 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Woda destylowana</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>6.8</v>
-      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
       <c r="D5" s="11">
         <f>IF(COUNTA(B5:C5)=0,"",AVERAGE(B5:C5))</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Badana próbka gleby</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
       <c r="D6" s="11">
         <f>IF(COUNTA(B6:C6)=0,"",AVERAGE(B6:C6))</f>
         <v/>
@@ -6318,34 +8041,26 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>KCl</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>7</v>
-      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
       <c r="D11" s="11">
         <f>IF(COUNTA(B11:C11)=0,"",AVERAGE(B11:C11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Badana próbka gleby</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>4.9</v>
-      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
       <c r="D12" s="11">
         <f>IF(COUNTA(B12:C12)=0,"",AVERAGE(B12:C12))</f>
         <v/>
@@ -6378,22 +8093,20 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>VNaOH</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>cm3</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>c_NaOH</t>
         </is>
@@ -6401,14 +8114,14 @@
       <c r="B18" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t>mol/dm3</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>k</t>
         </is>
@@ -6416,7 +8129,7 @@
       <c r="B19" s="6" t="n">
         <v>1.75</v>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t>współczynnik</t>
         </is>
@@ -6449,22 +8162,20 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>V_HCl</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="16" t="inlineStr">
         <is>
           <t>cm3</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>c_HCl</t>
         </is>
@@ -6472,29 +8183,27 @@
       <c r="B25" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>mol/dm3</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>V1_NaOH</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>cm3</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>c1_NaOH</t>
         </is>
@@ -6502,7 +8211,7 @@
       <c r="B27" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>mol/dm3</t>
         </is>
@@ -6535,7 +8244,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>p</t>
         </is>
@@ -6543,14 +8252,14 @@
       <c r="B32" s="6" t="n">
         <v>10000</v>
       </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C32" s="16" t="inlineStr">
         <is>
           <t>m2</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
@@ -6558,14 +8267,14 @@
       <c r="B33" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>rho</t>
         </is>
@@ -6573,7 +8282,7 @@
       <c r="B34" s="6" t="n">
         <v>1500</v>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>kg/m3</t>
         </is>
@@ -6592,7 +8301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6640,7 +8349,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Średnie pH wody destylowanej</t>
         </is>
@@ -6649,20 +8358,20 @@
         <f>IF(COUNTA(Gleba_Dane!B5:C5)=0,"",AVERAGE(Gleba_Dane!B5:C5))</f>
         <v/>
       </c>
-      <c r="C4" s="10" t="inlineStr"/>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr"/>
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>wartość pomocnicza</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
         <is>
           <t>Interpretacja</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Średnie pH próbki w wodzie</t>
         </is>
@@ -6671,20 +8380,20 @@
         <f>IF(COUNTA(Gleba_Dane!B6:C6)=0,"",AVERAGE(Gleba_Dane!B6:C6))</f>
         <v/>
       </c>
-      <c r="C5" s="10" t="inlineStr"/>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>kwasowość czynna</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>określ kategorię gleby</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Średnie pH KCl</t>
         </is>
@@ -6693,20 +8402,20 @@
         <f>IF(COUNTA(Gleba_Dane!B11:C11)=0,"",AVERAGE(Gleba_Dane!B11:C11))</f>
         <v/>
       </c>
-      <c r="C6" s="10" t="inlineStr"/>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>wartość pomocnicza</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>odnieś pH KCl do klasy gleby uprawnej i leśnej</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Średnie pH próbki w KCl</t>
         </is>
@@ -6715,20 +8424,20 @@
         <f>IF(COUNTA(Gleba_Dane!B12:C12)=0,"",AVERAGE(Gleba_Dane!B12:C12))</f>
         <v/>
       </c>
-      <c r="C7" s="10" t="inlineStr"/>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>podstawa klasyfikacji</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>skomentuj Hh, S i T</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Hh</t>
         </is>
@@ -6737,19 +8446,19 @@
         <f>IF(OR(Gleba_Dane!B17="",Gleba_Dane!B18="",Gleba_Dane!B19=""),"",Gleba_Dane!B17*Gleba_Dane!B18*10*Gleba_Dane!B19)</f>
         <v/>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>mmol(+)/100 g</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>kwasowość hydrolityczna</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Mz</t>
         </is>
@@ -6758,19 +8467,19 @@
         <f>IF(OR(Gleba_Dane!B32="",Gleba_Dane!B33="",Gleba_Dane!B34=""),"",Gleba_Dane!B32*Gleba_Dane!B33*Gleba_Dane!B34)</f>
         <v/>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>masa gleby dla 1 ha</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Hh_ha</t>
         </is>
@@ -6779,19 +8488,19 @@
         <f>IF(OR(B8="",B9=""),"",B8*B9/100)</f>
         <v/>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>mol(+)</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>całkowita kwasowość hydrolityczna</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>CaO</t>
         </is>
@@ -6800,19 +8509,19 @@
         <f>IF(B10="","",B10*0.028)</f>
         <v/>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>kg/ha</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>zapotrzebowanie na wapno</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>CaCO3</t>
         </is>
@@ -6821,19 +8530,19 @@
         <f>IF(B10="","",B10*0.05)</f>
         <v/>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>kg/ha</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>zapotrzebowanie na wapno</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -6842,19 +8551,19 @@
         <f>IF(OR(Gleba_Dane!B24="",Gleba_Dane!B25="",Gleba_Dane!B26="",Gleba_Dane!B27=""),"",(Gleba_Dane!B24*Gleba_Dane!B25-Gleba_Dane!B26*Gleba_Dane!B27)*4*5)</f>
         <v/>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>mmol(+)/100 g</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>suma kationów zasadowych</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
@@ -6863,19 +8572,19 @@
         <f>IF(OR(B8="",B13=""),"",B8+B13)</f>
         <v/>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>mmol(+)/100 g</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>pojemność sorpcyjna</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Klasa gleby uprawnej</t>
         </is>
@@ -6884,15 +8593,15 @@
         <f>IF(B7="","Brak danych",IF(B7&lt;=4,"bardzo kwaśne",IF(B7&lt;=4.5,"kwaśne",IF(B7&lt;=5,"średnio kwaśne",IF(B7&lt;=6,"słabo kwaśne",IF(B7&lt;=6.5,"obojętne",IF(B7&lt;=7,"słabo alkaliczne",IF(B7&lt;=7.5,"średnio alkaliczne","alkaliczne"))))))))</f>
         <v/>
       </c>
-      <c r="C15" s="10" t="inlineStr"/>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr"/>
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>klasyfikacja</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Klasa gleby leśnej</t>
         </is>
@@ -6901,8 +8610,8 @@
         <f>IF(B7="","Brak danych",IF(B7&lt;=3.5,"bardzo silnie kwaśne",IF(B7&lt;=4.5,"silnie kwaśne",IF(B7&lt;=5.5,"kwaśne",IF(B7&lt;=6.5,"słabo kwaśne",IF(B7&lt;=7.2,"obojętne",IF(B7&lt;=8,"słabo alkaliczne","alkaliczne")))))))</f>
         <v/>
       </c>
-      <c r="C16" s="10" t="inlineStr"/>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr"/>
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>klasyfikacja</t>
         </is>
@@ -6916,7 +8625,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6945,7 +8654,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>Wizualizacje pomocnicze</t>
         </is>
@@ -6953,7 +8662,7 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Porównanie pH</t>
         </is>
@@ -6961,7 +8670,7 @@
       <c r="B4" s="11" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Średnie pH wody destylowanej</t>
         </is>
@@ -6972,7 +8681,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Średnie pH próbki w wodzie</t>
         </is>
@@ -6983,7 +8692,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Średnie pH KCl</t>
         </is>
@@ -6994,7 +8703,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Średnie pH próbki w KCl</t>
         </is>
@@ -7008,7 +8717,7 @@
     <row r="10"/>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Hh vs S vs T</t>
         </is>
@@ -7016,7 +8725,7 @@
       <c r="B12" s="11" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Hh</t>
         </is>
@@ -7027,7 +8736,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -7038,7 +8747,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>T</t>
         </is>
@@ -7052,7 +8761,7 @@
     <row r="17"/>
     <row r="18"/>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>CaO vs CaCO3</t>
         </is>
@@ -7060,7 +8769,7 @@
       <c r="B19" s="11" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>CaO</t>
         </is>
@@ -7071,7 +8780,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>CaCO3</t>
         </is>
